--- a/reports/Debug-purgatory-20260105/purgatory_Report_20260105.xlsx
+++ b/reports/Debug-purgatory-20260105/purgatory_Report_20260105.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
   <si>
     <t>purgatory Resort
 Daily Management Report
@@ -103,15 +103,6 @@
     <t>FINANCIALS</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - Payroll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PR % of </t>
-  </si>
-  <si>
     <t>Mountain G&amp;A - Revenue</t>
   </si>
   <si>
@@ -569,15 +560,6 @@
   </si>
   <si>
     <t>PR % of IT Services</t>
-  </si>
-  <si>
-    <t>Durango Mountain Realty - Revenue</t>
-  </si>
-  <si>
-    <t>Durango Mountain Realty - Payroll</t>
-  </si>
-  <si>
-    <t>PR % of Durango Mountain Realty</t>
   </si>
   <si>
     <t>Pass-through Accounts - Revenue</t>
@@ -980,7 +962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N184"/>
+  <dimension ref="A1:N178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -1223,7 +1205,7 @@
         <v>11180</v>
       </c>
       <c r="L8" s="4">
-        <v>28793</v>
+        <v>28795</v>
       </c>
       <c r="M8" s="4">
         <v>50717</v>
@@ -1237,7 +1219,7 @@
         <v>20</v>
       </c>
       <c r="B9" s="4">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="C9" s="4">
         <v>1130</v>
@@ -1246,7 +1228,7 @@
         <v>1071</v>
       </c>
       <c r="E9" s="4">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="F9" s="4">
         <v>6506</v>
@@ -1258,7 +1240,7 @@
         <v>6383</v>
       </c>
       <c r="I9" s="4">
-        <v>6422</v>
+        <v>6419</v>
       </c>
       <c r="J9" s="4">
         <v>8472</v>
@@ -1267,7 +1249,7 @@
         <v>9071</v>
       </c>
       <c r="L9" s="4">
-        <v>28347</v>
+        <v>28344</v>
       </c>
       <c r="M9" s="4">
         <v>41262</v>
@@ -1325,7 +1307,7 @@
         <v>22</v>
       </c>
       <c r="B11" s="4">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="C11" s="4">
         <v>2444</v>
@@ -1334,7 +1316,7 @@
         <v>2415</v>
       </c>
       <c r="E11" s="4">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="F11" s="4">
         <v>18411</v>
@@ -1346,7 +1328,7 @@
         <v>19349</v>
       </c>
       <c r="I11" s="4">
-        <v>15319</v>
+        <v>15316</v>
       </c>
       <c r="J11" s="4">
         <v>21301</v>
@@ -1355,7 +1337,7 @@
         <v>24209</v>
       </c>
       <c r="L11" s="4">
-        <v>69332</v>
+        <v>69331</v>
       </c>
       <c r="M11" s="4">
         <v>102834</v>
@@ -1392,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="I14" s="4">
         <v>0</v>
@@ -1410,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1421,40 +1403,40 @@
         <v>0</v>
       </c>
       <c r="C15" s="4">
-        <v>0</v>
+        <v>377.99</v>
       </c>
       <c r="D15" s="4">
-        <v>0</v>
+        <v>290.04</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
       </c>
       <c r="F15" s="4">
-        <v>0</v>
+        <v>2485.93</v>
       </c>
       <c r="G15" s="4">
-        <v>0</v>
+        <v>290.04</v>
       </c>
       <c r="H15" s="4">
-        <v>0</v>
+        <v>2030.28</v>
       </c>
       <c r="I15" s="4">
         <v>0</v>
       </c>
       <c r="J15" s="4">
-        <v>0</v>
+        <v>1729.95</v>
       </c>
       <c r="K15" s="4">
-        <v>0</v>
+        <v>1450.2</v>
       </c>
       <c r="L15" s="4">
         <v>0</v>
       </c>
       <c r="M15" s="4">
-        <v>0</v>
+        <v>23347.34</v>
       </c>
       <c r="N15" s="4">
-        <v>0</v>
+        <v>19687.95</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1550,43 +1532,43 @@
         <v>28</v>
       </c>
       <c r="B18" s="4">
-        <v>297.92</v>
+        <v>448.7386111111111</v>
       </c>
       <c r="C18" s="4">
-        <v>377.99</v>
+        <v>4633.27</v>
       </c>
       <c r="D18" s="4">
-        <v>290.04</v>
+        <v>5093</v>
       </c>
       <c r="E18" s="4">
-        <v>297.92</v>
+        <v>448.7386111111111</v>
       </c>
       <c r="F18" s="4">
-        <v>2485.93</v>
+        <v>32142.69</v>
       </c>
       <c r="G18" s="4">
-        <v>290.04</v>
+        <v>5093</v>
       </c>
       <c r="H18" s="4">
-        <v>2030.28</v>
+        <v>37040.2</v>
       </c>
       <c r="I18" s="4">
-        <v>1489.6</v>
+        <v>2091.980416666667</v>
       </c>
       <c r="J18" s="4">
-        <v>1729.95</v>
+        <v>29323.85</v>
       </c>
       <c r="K18" s="4">
-        <v>1450.2</v>
+        <v>29567.68</v>
       </c>
       <c r="L18" s="4">
-        <v>19662.72</v>
+        <v>9378.051111111108</v>
       </c>
       <c r="M18" s="4">
-        <v>23347.34</v>
+        <v>196360.82</v>
       </c>
       <c r="N18" s="4">
-        <v>19687.95</v>
+        <v>225677.99</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1682,43 +1664,43 @@
         <v>31</v>
       </c>
       <c r="B21" s="4">
-        <v>3503.880402777779</v>
+        <v>0</v>
       </c>
       <c r="C21" s="4">
-        <v>4633.27</v>
+        <v>2673.06</v>
       </c>
       <c r="D21" s="4">
-        <v>5093</v>
+        <v>1862.3</v>
       </c>
       <c r="E21" s="4">
-        <v>3503.880402777778</v>
+        <v>0</v>
       </c>
       <c r="F21" s="4">
-        <v>32142.69</v>
+        <v>14457.75</v>
       </c>
       <c r="G21" s="4">
-        <v>5093</v>
+        <v>1862.3</v>
       </c>
       <c r="H21" s="4">
-        <v>37040.2</v>
+        <v>14997.24</v>
       </c>
       <c r="I21" s="4">
-        <v>21314.24007222222</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4">
-        <v>29323.85</v>
+        <v>10296.63</v>
       </c>
       <c r="K21" s="4">
-        <v>29567.68</v>
+        <v>11164.1</v>
       </c>
       <c r="L21" s="4">
-        <v>161770.4687361114</v>
+        <v>875.1436111111111</v>
       </c>
       <c r="M21" s="4">
-        <v>196360.82</v>
+        <v>136088.15</v>
       </c>
       <c r="N21" s="4">
-        <v>225677.99</v>
+        <v>139441.89</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1814,43 +1796,43 @@
         <v>34</v>
       </c>
       <c r="B24" s="4">
-        <v>2464.691986111111</v>
+        <v>0</v>
       </c>
       <c r="C24" s="4">
-        <v>2673.06</v>
+        <v>236.9</v>
       </c>
       <c r="D24" s="4">
-        <v>1862.3</v>
+        <v>2068.87</v>
       </c>
       <c r="E24" s="4">
-        <v>2464.691986111111</v>
+        <v>0</v>
       </c>
       <c r="F24" s="4">
-        <v>14457.75</v>
+        <v>947.6</v>
       </c>
       <c r="G24" s="4">
-        <v>1862.3</v>
+        <v>2068.87</v>
       </c>
       <c r="H24" s="4">
-        <v>14997.24</v>
+        <v>5953.26</v>
       </c>
       <c r="I24" s="4">
-        <v>9684.505116666665</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4">
-        <v>10296.63</v>
+        <v>7659.1</v>
       </c>
       <c r="K24" s="4">
-        <v>11164.1</v>
+        <v>4757.29</v>
       </c>
       <c r="L24" s="4">
-        <v>119708.7725777778</v>
+        <v>1228.501388888889</v>
       </c>
       <c r="M24" s="4">
-        <v>136088.15</v>
+        <v>119395.5</v>
       </c>
       <c r="N24" s="4">
-        <v>139441.89</v>
+        <v>97287.33</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1946,43 +1928,43 @@
         <v>37</v>
       </c>
       <c r="B27" s="4">
-        <v>1948.362988888889</v>
+        <v>0</v>
       </c>
       <c r="C27" s="4">
-        <v>236.9</v>
+        <v>906</v>
       </c>
       <c r="D27" s="4">
-        <v>2068.87</v>
+        <v>623.59</v>
       </c>
       <c r="E27" s="4">
-        <v>1948.362988888889</v>
+        <v>0</v>
       </c>
       <c r="F27" s="4">
-        <v>947.6</v>
+        <v>5690.3</v>
       </c>
       <c r="G27" s="4">
-        <v>2068.87</v>
+        <v>623.59</v>
       </c>
       <c r="H27" s="4">
-        <v>5953.26</v>
+        <v>5422.13</v>
       </c>
       <c r="I27" s="4">
-        <v>9155.433863888889</v>
+        <v>0</v>
       </c>
       <c r="J27" s="4">
-        <v>7659.1</v>
+        <v>3667.9</v>
       </c>
       <c r="K27" s="4">
-        <v>4757.29</v>
+        <v>3747.77</v>
       </c>
       <c r="L27" s="4">
-        <v>106808.5860666667</v>
+        <v>0</v>
       </c>
       <c r="M27" s="4">
-        <v>119395.5</v>
+        <v>40771.4</v>
       </c>
       <c r="N27" s="4">
-        <v>97287.33</v>
+        <v>41984.6</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2078,43 +2060,43 @@
         <v>40</v>
       </c>
       <c r="B30" s="4">
-        <v>860.0316666666666</v>
+        <v>211.235</v>
       </c>
       <c r="C30" s="4">
-        <v>906</v>
+        <v>2383.56</v>
       </c>
       <c r="D30" s="4">
-        <v>623.59</v>
+        <v>2159.55</v>
       </c>
       <c r="E30" s="4">
-        <v>860.0316666666666</v>
+        <v>211.235</v>
       </c>
       <c r="F30" s="4">
-        <v>5690.3</v>
+        <v>16444.3</v>
       </c>
       <c r="G30" s="4">
-        <v>623.59</v>
+        <v>2159.55</v>
       </c>
       <c r="H30" s="4">
-        <v>5422.13</v>
+        <v>13956.5</v>
       </c>
       <c r="I30" s="4">
-        <v>3424.361388888889</v>
+        <v>544.7611805555556</v>
       </c>
       <c r="J30" s="4">
-        <v>3667.9</v>
+        <v>11677.16</v>
       </c>
       <c r="K30" s="4">
-        <v>3747.77</v>
+        <v>11875.78</v>
       </c>
       <c r="L30" s="4">
-        <v>40539.18472222223</v>
+        <v>15311.05211111111</v>
       </c>
       <c r="M30" s="4">
-        <v>40771.4</v>
+        <v>127088.53</v>
       </c>
       <c r="N30" s="4">
-        <v>41984.6</v>
+        <v>115262.33</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2210,43 +2192,43 @@
         <v>43</v>
       </c>
       <c r="B33" s="4">
-        <v>1662.697777777778</v>
+        <v>0</v>
       </c>
       <c r="C33" s="4">
-        <v>2383.56</v>
+        <v>1050.93</v>
       </c>
       <c r="D33" s="4">
-        <v>2159.55</v>
+        <v>730.3200000000001</v>
       </c>
       <c r="E33" s="4">
-        <v>1662.697777777778</v>
+        <v>0</v>
       </c>
       <c r="F33" s="4">
-        <v>16444.3</v>
+        <v>9177.690000000001</v>
       </c>
       <c r="G33" s="4">
-        <v>2159.55</v>
+        <v>730.3200000000001</v>
       </c>
       <c r="H33" s="4">
-        <v>13956.5</v>
+        <v>6189.67</v>
       </c>
       <c r="I33" s="4">
-        <v>8585.712291666667</v>
+        <v>0</v>
       </c>
       <c r="J33" s="4">
-        <v>11677.16</v>
+        <v>5316.69</v>
       </c>
       <c r="K33" s="4">
-        <v>11875.78</v>
+        <v>4659.12</v>
       </c>
       <c r="L33" s="4">
-        <v>134875.1624444444</v>
+        <v>0</v>
       </c>
       <c r="M33" s="4">
-        <v>127088.53</v>
+        <v>87012.60000000001</v>
       </c>
       <c r="N33" s="4">
-        <v>115262.33</v>
+        <v>63171.85</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2342,43 +2324,43 @@
         <v>46</v>
       </c>
       <c r="B36" s="4">
-        <v>893.6025694444445</v>
+        <v>0</v>
       </c>
       <c r="C36" s="4">
-        <v>1050.93</v>
+        <v>3925.46</v>
       </c>
       <c r="D36" s="4">
-        <v>730.3200000000001</v>
+        <v>4194.74</v>
       </c>
       <c r="E36" s="4">
-        <v>893.6025694444445</v>
+        <v>0</v>
       </c>
       <c r="F36" s="4">
-        <v>9177.690000000001</v>
+        <v>30380.38</v>
       </c>
       <c r="G36" s="4">
-        <v>730.3200000000001</v>
+        <v>4194.74</v>
       </c>
       <c r="H36" s="4">
-        <v>6189.67</v>
+        <v>29999.4</v>
       </c>
       <c r="I36" s="4">
-        <v>6093.429102777778</v>
+        <v>0</v>
       </c>
       <c r="J36" s="4">
-        <v>5316.69</v>
+        <v>23686.26</v>
       </c>
       <c r="K36" s="4">
-        <v>4659.12</v>
+        <v>24148.58</v>
       </c>
       <c r="L36" s="4">
-        <v>79978.02996111111</v>
+        <v>419.7450333333333</v>
       </c>
       <c r="M36" s="4">
-        <v>87012.60000000001</v>
+        <v>213714.47</v>
       </c>
       <c r="N36" s="4">
-        <v>63171.85</v>
+        <v>217337.49</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2430,43 +2412,43 @@
         <v>48</v>
       </c>
       <c r="B38" s="4">
-        <v>0</v>
+        <v>91933.60000000001</v>
       </c>
       <c r="C38" s="4">
-        <v>0</v>
+        <v>181430.42</v>
       </c>
       <c r="D38" s="4">
-        <v>0</v>
+        <v>97871.13</v>
       </c>
       <c r="E38" s="4">
-        <v>0</v>
+        <v>91933.60000000001</v>
       </c>
       <c r="F38" s="4">
-        <v>0</v>
+        <v>1233730.74</v>
       </c>
       <c r="G38" s="4">
-        <v>0</v>
+        <v>97871.13</v>
       </c>
       <c r="H38" s="4">
-        <v>0</v>
+        <v>331031.4</v>
       </c>
       <c r="I38" s="4">
-        <v>0</v>
+        <v>802031.8199999999</v>
       </c>
       <c r="J38" s="4">
-        <v>0</v>
+        <v>1376599.82</v>
       </c>
       <c r="K38" s="4">
-        <v>0</v>
+        <v>406272.35</v>
       </c>
       <c r="L38" s="4">
-        <v>0</v>
+        <v>2504316.49</v>
       </c>
       <c r="M38" s="4">
-        <v>0</v>
+        <v>5934749.47</v>
       </c>
       <c r="N38" s="4">
-        <v>0</v>
+        <v>1563100.37</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2474,43 +2456,43 @@
         <v>49</v>
       </c>
       <c r="B39" s="4">
-        <v>3312.171716666667</v>
+        <v>166.3125</v>
       </c>
       <c r="C39" s="4">
-        <v>3925.46</v>
+        <v>1006.39</v>
       </c>
       <c r="D39" s="4">
-        <v>4194.74</v>
+        <v>1166.06</v>
       </c>
       <c r="E39" s="4">
-        <v>3312.171716666667</v>
+        <v>166.3125</v>
       </c>
       <c r="F39" s="4">
-        <v>30380.38</v>
+        <v>7543.03</v>
       </c>
       <c r="G39" s="4">
-        <v>4194.74</v>
+        <v>1166.06</v>
       </c>
       <c r="H39" s="4">
-        <v>29999.4</v>
+        <v>8242.940000000001</v>
       </c>
       <c r="I39" s="4">
-        <v>20142.353325</v>
+        <v>991.471527777778</v>
       </c>
       <c r="J39" s="4">
-        <v>23686.26</v>
+        <v>6902.99</v>
       </c>
       <c r="K39" s="4">
-        <v>24148.58</v>
+        <v>7532.55</v>
       </c>
       <c r="L39" s="4">
-        <v>162534.7397777778</v>
+        <v>6330.059583333335</v>
       </c>
       <c r="M39" s="4">
-        <v>213714.47</v>
+        <v>49038.69</v>
       </c>
       <c r="N39" s="4">
-        <v>217337.49</v>
+        <v>65157.82</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2518,43 +2500,43 @@
         <v>50</v>
       </c>
       <c r="B40" s="5">
-        <v>0</v>
+        <v>0.180905022755554</v>
       </c>
       <c r="C40" s="5">
-        <v>0</v>
+        <v>0.5546974978065971</v>
       </c>
       <c r="D40" s="5">
-        <v>0</v>
+        <v>1.191423865239933</v>
       </c>
       <c r="E40" s="5">
-        <v>0</v>
+        <v>0.180905022755554</v>
       </c>
       <c r="F40" s="5">
-        <v>0</v>
+        <v>0.6114000207208908</v>
       </c>
       <c r="G40" s="5">
-        <v>0</v>
+        <v>1.191423865239933</v>
       </c>
       <c r="H40" s="5">
-        <v>0</v>
+        <v>2.49007798051786</v>
       </c>
       <c r="I40" s="5">
-        <v>0</v>
+        <v>0.1236199740526227</v>
       </c>
       <c r="J40" s="5">
-        <v>0</v>
+        <v>0.5014521940007227</v>
       </c>
       <c r="K40" s="5">
-        <v>0</v>
+        <v>1.854064151793742</v>
       </c>
       <c r="L40" s="5">
-        <v>0</v>
+        <v>0.252765958640209</v>
       </c>
       <c r="M40" s="5">
-        <v>0</v>
+        <v>0.8262975589431242</v>
       </c>
       <c r="N40" s="5">
-        <v>0</v>
+        <v>4.168498789364371</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2562,43 +2544,43 @@
         <v>51</v>
       </c>
       <c r="B41" s="4">
-        <v>91933.60000000001</v>
+        <v>0</v>
       </c>
       <c r="C41" s="4">
-        <v>181430.42</v>
+        <v>0</v>
       </c>
       <c r="D41" s="4">
-        <v>181256.03</v>
+        <v>0</v>
       </c>
       <c r="E41" s="4">
-        <v>91933.60000000001</v>
+        <v>0</v>
       </c>
       <c r="F41" s="4">
-        <v>1233730.74</v>
+        <v>0</v>
       </c>
       <c r="G41" s="4">
-        <v>181256.03</v>
+        <v>0</v>
       </c>
       <c r="H41" s="4">
-        <v>1168872.42</v>
+        <v>0</v>
       </c>
       <c r="I41" s="4">
-        <v>802031.8199999999</v>
+        <v>0</v>
       </c>
       <c r="J41" s="4">
-        <v>1376599.82</v>
+        <v>0</v>
       </c>
       <c r="K41" s="4">
-        <v>1477828.6</v>
+        <v>0</v>
       </c>
       <c r="L41" s="4">
-        <v>2504316.49</v>
+        <v>0</v>
       </c>
       <c r="M41" s="4">
-        <v>5934749.47</v>
+        <v>0</v>
       </c>
       <c r="N41" s="4">
-        <v>5614287.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -2606,43 +2588,43 @@
         <v>52</v>
       </c>
       <c r="B42" s="4">
-        <v>3830.483127777778</v>
+        <v>0</v>
       </c>
       <c r="C42" s="4">
-        <v>1006.39</v>
+        <v>0</v>
       </c>
       <c r="D42" s="4">
-        <v>1166.06</v>
+        <v>0</v>
       </c>
       <c r="E42" s="4">
-        <v>3830.483127777778</v>
+        <v>0</v>
       </c>
       <c r="F42" s="4">
-        <v>7543.03</v>
+        <v>0</v>
       </c>
       <c r="G42" s="4">
-        <v>1166.06</v>
+        <v>0</v>
       </c>
       <c r="H42" s="4">
-        <v>8242.940000000001</v>
+        <v>0</v>
       </c>
       <c r="I42" s="4">
-        <v>23185.81536111112</v>
+        <v>0</v>
       </c>
       <c r="J42" s="4">
-        <v>6902.99</v>
+        <v>0</v>
       </c>
       <c r="K42" s="4">
-        <v>7532.55</v>
+        <v>0</v>
       </c>
       <c r="L42" s="4">
-        <v>176392.8854333334</v>
+        <v>0</v>
       </c>
       <c r="M42" s="4">
-        <v>49038.69</v>
+        <v>0</v>
       </c>
       <c r="N42" s="4">
-        <v>65157.82</v>
+        <v>1557.58</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -2650,43 +2632,43 @@
         <v>53</v>
       </c>
       <c r="B43" s="5">
-        <v>4.166575797943056</v>
+        <v>0</v>
       </c>
       <c r="C43" s="5">
-        <v>0.5546974978065971</v>
+        <v>0</v>
       </c>
       <c r="D43" s="5">
-        <v>0.6433220456169099</v>
+        <v>0</v>
       </c>
       <c r="E43" s="5">
-        <v>4.166575797943056</v>
+        <v>0</v>
       </c>
       <c r="F43" s="5">
-        <v>0.6114000207208908</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5">
-        <v>0.6433220456169099</v>
+        <v>0</v>
       </c>
       <c r="H43" s="5">
-        <v>0.7052044225664936</v>
+        <v>0</v>
       </c>
       <c r="I43" s="5">
-        <v>2.890884723390541</v>
+        <v>0</v>
       </c>
       <c r="J43" s="5">
-        <v>0.5014521940007227</v>
+        <v>0</v>
       </c>
       <c r="K43" s="5">
-        <v>0.5097038993561229</v>
+        <v>0</v>
       </c>
       <c r="L43" s="5">
-        <v>7.043554045093295</v>
+        <v>0</v>
       </c>
       <c r="M43" s="5">
-        <v>0.8262975589431242</v>
+        <v>0</v>
       </c>
       <c r="N43" s="5">
-        <v>1.160571506972423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -2694,43 +2676,43 @@
         <v>54</v>
       </c>
       <c r="B44" s="4">
-        <v>0</v>
+        <v>31417.3</v>
       </c>
       <c r="C44" s="4">
-        <v>0</v>
+        <v>26555</v>
       </c>
       <c r="D44" s="4">
-        <v>0</v>
+        <v>26997.33</v>
       </c>
       <c r="E44" s="4">
-        <v>0</v>
+        <v>31417.3</v>
       </c>
       <c r="F44" s="4">
-        <v>0</v>
+        <v>152890.98</v>
       </c>
       <c r="G44" s="4">
-        <v>0</v>
+        <v>26997.33</v>
       </c>
       <c r="H44" s="4">
-        <v>0</v>
+        <v>126157.95</v>
       </c>
       <c r="I44" s="4">
-        <v>0</v>
+        <v>180380.86</v>
       </c>
       <c r="J44" s="4">
-        <v>0</v>
+        <v>224789</v>
       </c>
       <c r="K44" s="4">
-        <v>0</v>
+        <v>274672.12</v>
       </c>
       <c r="L44" s="4">
-        <v>0</v>
+        <v>732600.9300000001</v>
       </c>
       <c r="M44" s="4">
-        <v>0</v>
+        <v>1068972.94</v>
       </c>
       <c r="N44" s="4">
-        <v>0</v>
+        <v>811148.97</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -2738,43 +2720,43 @@
         <v>55</v>
       </c>
       <c r="B45" s="4">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="C45" s="4">
-        <v>0</v>
+        <v>5941.92</v>
       </c>
       <c r="D45" s="4">
-        <v>0</v>
+        <v>10801.46</v>
       </c>
       <c r="E45" s="4">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="F45" s="4">
-        <v>0</v>
+        <v>34935.56</v>
       </c>
       <c r="G45" s="4">
-        <v>0</v>
+        <v>10801.46</v>
       </c>
       <c r="H45" s="4">
-        <v>0</v>
+        <v>43706.53</v>
       </c>
       <c r="I45" s="4">
-        <v>0</v>
+        <v>4005.903194444444</v>
       </c>
       <c r="J45" s="4">
-        <v>0</v>
+        <v>43847.49</v>
       </c>
       <c r="K45" s="4">
-        <v>0</v>
+        <v>47561.3</v>
       </c>
       <c r="L45" s="4">
-        <v>0</v>
+        <v>20217.96930555555</v>
       </c>
       <c r="M45" s="4">
-        <v>0</v>
+        <v>238118.31</v>
       </c>
       <c r="N45" s="4">
-        <v>1557.58</v>
+        <v>248558.38</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -2782,43 +2764,43 @@
         <v>56</v>
       </c>
       <c r="B46" s="5">
-        <v>0</v>
+        <v>1.543735457852839</v>
       </c>
       <c r="C46" s="5">
-        <v>0</v>
+        <v>22.37589907738656</v>
       </c>
       <c r="D46" s="5">
-        <v>0</v>
+        <v>40.00936388894753</v>
       </c>
       <c r="E46" s="5">
-        <v>0</v>
+        <v>1.543735457852839</v>
       </c>
       <c r="F46" s="5">
-        <v>0</v>
+        <v>22.84998107802043</v>
       </c>
       <c r="G46" s="5">
-        <v>0</v>
+        <v>40.00936388894753</v>
       </c>
       <c r="H46" s="5">
-        <v>0</v>
+        <v>34.64429312619617</v>
       </c>
       <c r="I46" s="5">
-        <v>0</v>
+        <v>2.220802802716677</v>
       </c>
       <c r="J46" s="5">
-        <v>0</v>
+        <v>19.50606568826766</v>
       </c>
       <c r="K46" s="5">
-        <v>0</v>
+        <v>17.31566348998217</v>
       </c>
       <c r="L46" s="5">
-        <v>0</v>
+        <v>2.759752066593139</v>
       </c>
       <c r="M46" s="5">
-        <v>0</v>
+        <v>22.27542916100384</v>
       </c>
       <c r="N46" s="5">
-        <v>0</v>
+        <v>30.64275357459925</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -2826,43 +2808,43 @@
         <v>57</v>
       </c>
       <c r="B47" s="4">
-        <v>31417.3</v>
+        <v>800</v>
       </c>
       <c r="C47" s="4">
-        <v>26555</v>
+        <v>659.88</v>
       </c>
       <c r="D47" s="4">
-        <v>26997.33</v>
+        <v>500</v>
       </c>
       <c r="E47" s="4">
-        <v>31417.3</v>
+        <v>800</v>
       </c>
       <c r="F47" s="4">
-        <v>152890.98</v>
+        <v>4970.97</v>
       </c>
       <c r="G47" s="4">
-        <v>26997.33</v>
+        <v>500</v>
       </c>
       <c r="H47" s="4">
-        <v>153155.28</v>
+        <v>3784</v>
       </c>
       <c r="I47" s="4">
-        <v>180380.86</v>
+        <v>5600</v>
       </c>
       <c r="J47" s="4">
-        <v>224789</v>
+        <v>5751.27</v>
       </c>
       <c r="K47" s="4">
-        <v>274672.12</v>
+        <v>7660</v>
       </c>
       <c r="L47" s="4">
-        <v>732600.9300000001</v>
+        <v>20600</v>
       </c>
       <c r="M47" s="4">
-        <v>1068972.94</v>
+        <v>27765.18</v>
       </c>
       <c r="N47" s="4">
-        <v>870860.21</v>
+        <v>23600</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -2870,43 +2852,43 @@
         <v>58</v>
       </c>
       <c r="B48" s="4">
-        <v>5359.309999999999</v>
+        <v>0</v>
       </c>
       <c r="C48" s="4">
-        <v>5941.92</v>
+        <v>266.97</v>
       </c>
       <c r="D48" s="4">
-        <v>10801.46</v>
+        <v>334.75</v>
       </c>
       <c r="E48" s="4">
-        <v>5359.31</v>
+        <v>0</v>
       </c>
       <c r="F48" s="4">
-        <v>34935.56</v>
+        <v>1962.54</v>
       </c>
       <c r="G48" s="4">
-        <v>10801.46</v>
+        <v>334.75</v>
       </c>
       <c r="H48" s="4">
-        <v>43706.53</v>
+        <v>2414.5</v>
       </c>
       <c r="I48" s="4">
-        <v>30148.44602777778</v>
+        <v>0</v>
       </c>
       <c r="J48" s="4">
-        <v>43847.49</v>
+        <v>2339.85</v>
       </c>
       <c r="K48" s="4">
-        <v>47561.3</v>
+        <v>1642.49</v>
       </c>
       <c r="L48" s="4">
-        <v>208142.2371055553</v>
+        <v>811.51125</v>
       </c>
       <c r="M48" s="4">
-        <v>238118.31</v>
+        <v>15104.79</v>
       </c>
       <c r="N48" s="4">
-        <v>248558.38</v>
+        <v>14923.37</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -2914,43 +2896,43 @@
         <v>59</v>
       </c>
       <c r="B49" s="5">
-        <v>17.05846778685628</v>
+        <v>0</v>
       </c>
       <c r="C49" s="5">
-        <v>22.37589907738656</v>
+        <v>40.4573558828878</v>
       </c>
       <c r="D49" s="5">
-        <v>40.00936388894753</v>
+        <v>66.95</v>
       </c>
       <c r="E49" s="5">
-        <v>17.05846778685629</v>
+        <v>0</v>
       </c>
       <c r="F49" s="5">
-        <v>22.84998107802043</v>
+        <v>39.48002100193725</v>
       </c>
       <c r="G49" s="5">
-        <v>40.00936388894753</v>
+        <v>66.95</v>
       </c>
       <c r="H49" s="5">
-        <v>28.53739681713879</v>
+        <v>63.80813953488372</v>
       </c>
       <c r="I49" s="5">
-        <v>16.71377219721526</v>
+        <v>0</v>
       </c>
       <c r="J49" s="5">
-        <v>19.50606568826766</v>
+        <v>40.68405760814567</v>
       </c>
       <c r="K49" s="5">
-        <v>17.31566348998217</v>
+        <v>21.44242819843342</v>
       </c>
       <c r="L49" s="5">
-        <v>28.41140770945449</v>
+        <v>3.939375</v>
       </c>
       <c r="M49" s="5">
-        <v>22.27542916100384</v>
+        <v>54.40191635710627</v>
       </c>
       <c r="N49" s="5">
-        <v>28.54170820366222</v>
+        <v>63.23461864406779</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -2958,43 +2940,43 @@
         <v>60</v>
       </c>
       <c r="B50" s="4">
-        <v>800</v>
+        <v>46562.02</v>
       </c>
       <c r="C50" s="4">
-        <v>659.88</v>
+        <v>28758.5</v>
       </c>
       <c r="D50" s="4">
-        <v>500</v>
+        <v>41759</v>
       </c>
       <c r="E50" s="4">
-        <v>800</v>
+        <v>46562.02</v>
       </c>
       <c r="F50" s="4">
-        <v>4970.97</v>
+        <v>165577.7</v>
       </c>
       <c r="G50" s="4">
-        <v>500</v>
+        <v>41759</v>
       </c>
       <c r="H50" s="4">
-        <v>3784</v>
+        <v>131238.08</v>
       </c>
       <c r="I50" s="4">
-        <v>5600</v>
+        <v>202478.06</v>
       </c>
       <c r="J50" s="4">
-        <v>5751.27</v>
+        <v>215612.4</v>
       </c>
       <c r="K50" s="4">
-        <v>7660</v>
+        <v>195901.83</v>
       </c>
       <c r="L50" s="4">
-        <v>20600</v>
+        <v>832291.7</v>
       </c>
       <c r="M50" s="4">
-        <v>27765.18</v>
+        <v>1050117.9</v>
       </c>
       <c r="N50" s="4">
-        <v>23600</v>
+        <v>911183.14</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -3002,43 +2984,43 @@
         <v>61</v>
       </c>
       <c r="B51" s="4">
-        <v>416.7183333333333</v>
+        <v>0</v>
       </c>
       <c r="C51" s="4">
-        <v>266.97</v>
+        <v>1783.26</v>
       </c>
       <c r="D51" s="4">
-        <v>334.75</v>
+        <v>1375.17</v>
       </c>
       <c r="E51" s="4">
-        <v>416.7183333333333</v>
+        <v>0</v>
       </c>
       <c r="F51" s="4">
-        <v>1962.54</v>
+        <v>12017.3</v>
       </c>
       <c r="G51" s="4">
-        <v>334.75</v>
+        <v>1375.17</v>
       </c>
       <c r="H51" s="4">
-        <v>2414.5</v>
+        <v>8982.610000000001</v>
       </c>
       <c r="I51" s="4">
-        <v>1796.033333333333</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4">
-        <v>2339.85</v>
+        <v>11548.3</v>
       </c>
       <c r="K51" s="4">
-        <v>1642.49</v>
+        <v>8990.82</v>
       </c>
       <c r="L51" s="4">
-        <v>12803.95416666667</v>
+        <v>0</v>
       </c>
       <c r="M51" s="4">
-        <v>15104.79</v>
+        <v>75383.48</v>
       </c>
       <c r="N51" s="4">
-        <v>14923.37</v>
+        <v>75651.41</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -3046,43 +3028,43 @@
         <v>62</v>
       </c>
       <c r="B52" s="5">
-        <v>52.08979166666666</v>
+        <v>0</v>
       </c>
       <c r="C52" s="5">
-        <v>40.4573558828878</v>
+        <v>6.200810195246623</v>
       </c>
       <c r="D52" s="5">
-        <v>66.95</v>
+        <v>3.293110467204675</v>
       </c>
       <c r="E52" s="5">
-        <v>52.08979166666666</v>
+        <v>0</v>
       </c>
       <c r="F52" s="5">
-        <v>39.48002100193725</v>
+        <v>7.257801020306477</v>
       </c>
       <c r="G52" s="5">
-        <v>66.95</v>
+        <v>3.293110467204675</v>
       </c>
       <c r="H52" s="5">
-        <v>63.80813953488372</v>
+        <v>6.844514945662114</v>
       </c>
       <c r="I52" s="5">
-        <v>32.07202380952381</v>
+        <v>0</v>
       </c>
       <c r="J52" s="5">
-        <v>40.68405760814567</v>
+        <v>5.35604631273526</v>
       </c>
       <c r="K52" s="5">
-        <v>21.44242819843342</v>
+        <v>4.589451767755309</v>
       </c>
       <c r="L52" s="5">
-        <v>62.15511731391585</v>
+        <v>0</v>
       </c>
       <c r="M52" s="5">
-        <v>54.40191635710627</v>
+        <v>7.178572996422592</v>
       </c>
       <c r="N52" s="5">
-        <v>63.23461864406779</v>
+        <v>8.302547169606321</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -3090,43 +3072,43 @@
         <v>63</v>
       </c>
       <c r="B53" s="4">
-        <v>46562.02</v>
+        <v>0</v>
       </c>
       <c r="C53" s="4">
-        <v>28758.5</v>
+        <v>0</v>
       </c>
       <c r="D53" s="4">
-        <v>41759</v>
+        <v>0</v>
       </c>
       <c r="E53" s="4">
-        <v>46562.02</v>
+        <v>0</v>
       </c>
       <c r="F53" s="4">
-        <v>165577.7</v>
+        <v>0</v>
       </c>
       <c r="G53" s="4">
-        <v>41759</v>
+        <v>0</v>
       </c>
       <c r="H53" s="4">
-        <v>172997.08</v>
+        <v>0</v>
       </c>
       <c r="I53" s="4">
-        <v>202478.06</v>
+        <v>0</v>
       </c>
       <c r="J53" s="4">
-        <v>215612.4</v>
+        <v>0</v>
       </c>
       <c r="K53" s="4">
-        <v>195901.83</v>
+        <v>0</v>
       </c>
       <c r="L53" s="4">
-        <v>832291.7</v>
+        <v>0</v>
       </c>
       <c r="M53" s="4">
-        <v>1050117.9</v>
+        <v>0</v>
       </c>
       <c r="N53" s="4">
-        <v>970120.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -3137,40 +3119,40 @@
         <v>0</v>
       </c>
       <c r="C54" s="4">
-        <v>1783.26</v>
+        <v>0</v>
       </c>
       <c r="D54" s="4">
-        <v>1375.17</v>
+        <v>0</v>
       </c>
       <c r="E54" s="4">
         <v>0</v>
       </c>
       <c r="F54" s="4">
-        <v>12017.3</v>
+        <v>0</v>
       </c>
       <c r="G54" s="4">
-        <v>1375.17</v>
+        <v>0</v>
       </c>
       <c r="H54" s="4">
-        <v>8982.610000000001</v>
+        <v>0</v>
       </c>
       <c r="I54" s="4">
         <v>0</v>
       </c>
       <c r="J54" s="4">
-        <v>11548.3</v>
+        <v>0</v>
       </c>
       <c r="K54" s="4">
-        <v>8990.82</v>
+        <v>0</v>
       </c>
       <c r="L54" s="4">
-        <v>7000.417127777776</v>
+        <v>0</v>
       </c>
       <c r="M54" s="4">
-        <v>75383.48</v>
+        <v>0</v>
       </c>
       <c r="N54" s="4">
-        <v>75651.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -3181,40 +3163,40 @@
         <v>0</v>
       </c>
       <c r="C55" s="5">
-        <v>6.200810195246623</v>
+        <v>0</v>
       </c>
       <c r="D55" s="5">
-        <v>3.293110467204675</v>
+        <v>0</v>
       </c>
       <c r="E55" s="5">
         <v>0</v>
       </c>
       <c r="F55" s="5">
-        <v>7.257801020306477</v>
+        <v>0</v>
       </c>
       <c r="G55" s="5">
-        <v>3.293110467204675</v>
+        <v>0</v>
       </c>
       <c r="H55" s="5">
-        <v>5.192347755233788</v>
+        <v>0</v>
       </c>
       <c r="I55" s="5">
         <v>0</v>
       </c>
       <c r="J55" s="5">
-        <v>5.35604631273526</v>
+        <v>0</v>
       </c>
       <c r="K55" s="5">
-        <v>4.589451767755309</v>
+        <v>0</v>
       </c>
       <c r="L55" s="5">
-        <v>0.8411013984373239</v>
+        <v>0</v>
       </c>
       <c r="M55" s="5">
-        <v>7.178572996422592</v>
+        <v>0</v>
       </c>
       <c r="N55" s="5">
-        <v>7.79814890960408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -3222,43 +3204,43 @@
         <v>66</v>
       </c>
       <c r="B56" s="4">
-        <v>0</v>
+        <v>6719.14</v>
       </c>
       <c r="C56" s="4">
-        <v>0</v>
+        <v>2566.18</v>
       </c>
       <c r="D56" s="4">
-        <v>0</v>
+        <v>6849.84</v>
       </c>
       <c r="E56" s="4">
-        <v>0</v>
+        <v>6719.14</v>
       </c>
       <c r="F56" s="4">
-        <v>0</v>
+        <v>19331.46</v>
       </c>
       <c r="G56" s="4">
-        <v>0</v>
+        <v>6849.84</v>
       </c>
       <c r="H56" s="4">
-        <v>0</v>
+        <v>17037.88</v>
       </c>
       <c r="I56" s="4">
-        <v>0</v>
+        <v>15791.18</v>
       </c>
       <c r="J56" s="4">
-        <v>0</v>
+        <v>22365.99</v>
       </c>
       <c r="K56" s="4">
-        <v>0</v>
+        <v>16351.69</v>
       </c>
       <c r="L56" s="4">
-        <v>0</v>
+        <v>66086.03999999999</v>
       </c>
       <c r="M56" s="4">
-        <v>0</v>
+        <v>107975.13</v>
       </c>
       <c r="N56" s="4">
-        <v>2</v>
+        <v>95672.48</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -3269,40 +3251,40 @@
         <v>0</v>
       </c>
       <c r="C57" s="4">
-        <v>0</v>
+        <v>586.26</v>
       </c>
       <c r="D57" s="4">
-        <v>0</v>
+        <v>118.13</v>
       </c>
       <c r="E57" s="4">
         <v>0</v>
       </c>
       <c r="F57" s="4">
-        <v>0</v>
+        <v>3830.8</v>
       </c>
       <c r="G57" s="4">
-        <v>0</v>
+        <v>118.13</v>
       </c>
       <c r="H57" s="4">
-        <v>0</v>
+        <v>432.03</v>
       </c>
       <c r="I57" s="4">
         <v>0</v>
       </c>
       <c r="J57" s="4">
-        <v>0</v>
+        <v>3025.78</v>
       </c>
       <c r="K57" s="4">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="L57" s="4">
         <v>0</v>
       </c>
       <c r="M57" s="4">
-        <v>0</v>
+        <v>26362.48</v>
       </c>
       <c r="N57" s="4">
-        <v>0</v>
+        <v>5525.28</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3313,40 +3295,40 @@
         <v>0</v>
       </c>
       <c r="C58" s="5">
-        <v>0</v>
+        <v>22.84563047019305</v>
       </c>
       <c r="D58" s="5">
-        <v>0</v>
+        <v>1.724565829274844</v>
       </c>
       <c r="E58" s="5">
         <v>0</v>
       </c>
       <c r="F58" s="5">
-        <v>0</v>
+        <v>19.81640289972925</v>
       </c>
       <c r="G58" s="5">
-        <v>0</v>
+        <v>1.724565829274844</v>
       </c>
       <c r="H58" s="5">
-        <v>0</v>
+        <v>2.535702798705003</v>
       </c>
       <c r="I58" s="5">
         <v>0</v>
       </c>
       <c r="J58" s="5">
-        <v>0</v>
+        <v>13.52848677836304</v>
       </c>
       <c r="K58" s="5">
-        <v>0</v>
+        <v>0.770562553473066</v>
       </c>
       <c r="L58" s="5">
         <v>0</v>
       </c>
       <c r="M58" s="5">
-        <v>0</v>
+        <v>24.41532601072117</v>
       </c>
       <c r="N58" s="5">
-        <v>0</v>
+        <v>5.775203067799644</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3354,43 +3336,43 @@
         <v>69</v>
       </c>
       <c r="B59" s="4">
-        <v>6719.14</v>
+        <v>14987.44</v>
       </c>
       <c r="C59" s="4">
-        <v>2566.18</v>
+        <v>12200.43</v>
       </c>
       <c r="D59" s="4">
-        <v>6849.84</v>
+        <v>10007.03</v>
       </c>
       <c r="E59" s="4">
-        <v>6719.14</v>
+        <v>14987.44</v>
       </c>
       <c r="F59" s="4">
-        <v>19331.46</v>
+        <v>91907.63</v>
       </c>
       <c r="G59" s="4">
-        <v>6849.84</v>
+        <v>10007.03</v>
       </c>
       <c r="H59" s="4">
-        <v>23887.72</v>
+        <v>65571.25999999999</v>
       </c>
       <c r="I59" s="4">
-        <v>15791.18</v>
+        <v>72074.07000000001</v>
       </c>
       <c r="J59" s="4">
-        <v>22365.99</v>
+        <v>106334.53</v>
       </c>
       <c r="K59" s="4">
-        <v>16351.69</v>
+        <v>71419.64</v>
       </c>
       <c r="L59" s="4">
-        <v>66086.03999999999</v>
+        <v>327086.99</v>
       </c>
       <c r="M59" s="4">
-        <v>107975.13</v>
+        <v>513346.83</v>
       </c>
       <c r="N59" s="4">
-        <v>99692.89</v>
+        <v>492093.2</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3398,43 +3380,43 @@
         <v>70</v>
       </c>
       <c r="B60" s="4">
-        <v>0</v>
+        <v>73.625</v>
       </c>
       <c r="C60" s="4">
-        <v>586.26</v>
+        <v>579.26</v>
       </c>
       <c r="D60" s="4">
-        <v>118.13</v>
+        <v>1678.25</v>
       </c>
       <c r="E60" s="4">
-        <v>0</v>
+        <v>73.625</v>
       </c>
       <c r="F60" s="4">
-        <v>3830.8</v>
+        <v>3774.8</v>
       </c>
       <c r="G60" s="4">
-        <v>118.13</v>
+        <v>1678.25</v>
       </c>
       <c r="H60" s="4">
-        <v>432.03</v>
+        <v>10632.17</v>
       </c>
       <c r="I60" s="4">
-        <v>0</v>
+        <v>99.675</v>
       </c>
       <c r="J60" s="4">
-        <v>3025.78</v>
+        <v>3032.78</v>
       </c>
       <c r="K60" s="4">
-        <v>126</v>
+        <v>6594.17</v>
       </c>
       <c r="L60" s="4">
-        <v>0</v>
+        <v>303.5833333333333</v>
       </c>
       <c r="M60" s="4">
-        <v>26362.48</v>
+        <v>24979.96</v>
       </c>
       <c r="N60" s="4">
-        <v>5525.28</v>
+        <v>51272.3</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3442,43 +3424,43 @@
         <v>71</v>
       </c>
       <c r="B61" s="5">
-        <v>0</v>
+        <v>0.4912446688693999</v>
       </c>
       <c r="C61" s="5">
-        <v>22.84563047019305</v>
+        <v>4.747865444086806</v>
       </c>
       <c r="D61" s="5">
-        <v>1.724565829274844</v>
+        <v>16.77071019073591</v>
       </c>
       <c r="E61" s="5">
-        <v>0</v>
+        <v>0.4912446688693999</v>
       </c>
       <c r="F61" s="5">
-        <v>19.81640289972925</v>
+        <v>4.107167163379144</v>
       </c>
       <c r="G61" s="5">
-        <v>1.724565829274844</v>
+        <v>16.77071019073591</v>
       </c>
       <c r="H61" s="5">
-        <v>1.808586168960453</v>
+        <v>16.21468002902492</v>
       </c>
       <c r="I61" s="5">
-        <v>0</v>
+        <v>0.1382952287833891</v>
       </c>
       <c r="J61" s="5">
-        <v>13.52848677836304</v>
+        <v>2.85211210318981</v>
       </c>
       <c r="K61" s="5">
-        <v>0.770562553473066</v>
+        <v>9.232992493381373</v>
       </c>
       <c r="L61" s="5">
-        <v>0</v>
+        <v>0.09281424899637043</v>
       </c>
       <c r="M61" s="5">
-        <v>24.41532601072117</v>
+        <v>4.866098033565338</v>
       </c>
       <c r="N61" s="5">
-        <v>5.542300960479729</v>
+        <v>10.41922546379426</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3486,43 +3468,43 @@
         <v>72</v>
       </c>
       <c r="B62" s="4">
-        <v>14987.44</v>
+        <v>1448.57</v>
       </c>
       <c r="C62" s="4">
-        <v>12200.43</v>
+        <v>3900.99</v>
       </c>
       <c r="D62" s="4">
-        <v>10007.03</v>
+        <v>1213.89</v>
       </c>
       <c r="E62" s="4">
-        <v>14987.44</v>
+        <v>1448.57</v>
       </c>
       <c r="F62" s="4">
-        <v>91907.63</v>
+        <v>25975.73</v>
       </c>
       <c r="G62" s="4">
-        <v>10007.03</v>
+        <v>1213.89</v>
       </c>
       <c r="H62" s="4">
-        <v>75578.28999999999</v>
+        <v>12177.7</v>
       </c>
       <c r="I62" s="4">
-        <v>72074.07000000001</v>
+        <v>23385.65</v>
       </c>
       <c r="J62" s="4">
-        <v>106334.53</v>
+        <v>31659.4</v>
       </c>
       <c r="K62" s="4">
-        <v>71419.64</v>
+        <v>26891.17</v>
       </c>
       <c r="L62" s="4">
-        <v>327086.99</v>
+        <v>129440</v>
       </c>
       <c r="M62" s="4">
-        <v>513346.83</v>
+        <v>166363.98</v>
       </c>
       <c r="N62" s="4">
-        <v>518349.15</v>
+        <v>179889.5</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3530,43 +3512,43 @@
         <v>73</v>
       </c>
       <c r="B63" s="4">
-        <v>146.065</v>
+        <v>0</v>
       </c>
       <c r="C63" s="4">
-        <v>579.26</v>
+        <v>649.76</v>
       </c>
       <c r="D63" s="4">
-        <v>1678.25</v>
+        <v>562.6900000000001</v>
       </c>
       <c r="E63" s="4">
-        <v>146.065</v>
+        <v>0</v>
       </c>
       <c r="F63" s="4">
-        <v>3774.8</v>
+        <v>4284.8</v>
       </c>
       <c r="G63" s="4">
-        <v>1678.25</v>
+        <v>562.6900000000001</v>
       </c>
       <c r="H63" s="4">
-        <v>10632.17</v>
+        <v>4014.51</v>
       </c>
       <c r="I63" s="4">
-        <v>320.205</v>
+        <v>0</v>
       </c>
       <c r="J63" s="4">
-        <v>3032.78</v>
+        <v>3941.28</v>
       </c>
       <c r="K63" s="4">
-        <v>6594.17</v>
+        <v>3078.95</v>
       </c>
       <c r="L63" s="4">
-        <v>9081.813822222219</v>
+        <v>135.0833333333333</v>
       </c>
       <c r="M63" s="4">
-        <v>24979.96</v>
+        <v>29187.84</v>
       </c>
       <c r="N63" s="4">
-        <v>51272.3</v>
+        <v>36580.54</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3574,43 +3556,43 @@
         <v>74</v>
       </c>
       <c r="B64" s="5">
-        <v>0.9745827172619206</v>
+        <v>0</v>
       </c>
       <c r="C64" s="5">
-        <v>4.747865444086806</v>
+        <v>16.65628468670774</v>
       </c>
       <c r="D64" s="5">
-        <v>16.77071019073591</v>
+        <v>46.35428251324255</v>
       </c>
       <c r="E64" s="5">
-        <v>0.9745827172619206</v>
+        <v>0</v>
       </c>
       <c r="F64" s="5">
-        <v>4.107167163379144</v>
+        <v>16.49539781942606</v>
       </c>
       <c r="G64" s="5">
-        <v>16.77071019073591</v>
+        <v>46.35428251324255</v>
       </c>
       <c r="H64" s="5">
-        <v>14.06775675924925</v>
+        <v>32.96607733808519</v>
       </c>
       <c r="I64" s="5">
-        <v>0.4442721217214456</v>
+        <v>0</v>
       </c>
       <c r="J64" s="5">
-        <v>2.85211210318981</v>
+        <v>12.44900408725371</v>
       </c>
       <c r="K64" s="5">
-        <v>9.232992493381373</v>
+        <v>11.44966916649592</v>
       </c>
       <c r="L64" s="5">
-        <v>2.776574458746347</v>
+        <v>0.1043598063452822</v>
       </c>
       <c r="M64" s="5">
-        <v>4.866098033565338</v>
+        <v>17.54456703909103</v>
       </c>
       <c r="N64" s="5">
-        <v>9.891460225216923</v>
+        <v>20.33500565625009</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -3618,43 +3600,43 @@
         <v>75</v>
       </c>
       <c r="B65" s="4">
-        <v>1448.57</v>
+        <v>3921.86</v>
       </c>
       <c r="C65" s="4">
-        <v>3900.99</v>
+        <v>4379.63</v>
       </c>
       <c r="D65" s="4">
-        <v>1213.89</v>
+        <v>2679.72</v>
       </c>
       <c r="E65" s="4">
-        <v>1448.57</v>
+        <v>3921.86</v>
       </c>
       <c r="F65" s="4">
-        <v>25975.73</v>
+        <v>32992.4</v>
       </c>
       <c r="G65" s="4">
-        <v>1213.89</v>
+        <v>2679.72</v>
       </c>
       <c r="H65" s="4">
-        <v>13391.59</v>
+        <v>18675.71</v>
       </c>
       <c r="I65" s="4">
-        <v>23385.65</v>
+        <v>33099.05</v>
       </c>
       <c r="J65" s="4">
-        <v>31659.4</v>
+        <v>38171.3</v>
       </c>
       <c r="K65" s="4">
-        <v>26891.17</v>
+        <v>30386.91</v>
       </c>
       <c r="L65" s="4">
-        <v>129440</v>
+        <v>128420.01</v>
       </c>
       <c r="M65" s="4">
-        <v>166363.98</v>
+        <v>184277.65</v>
       </c>
       <c r="N65" s="4">
-        <v>187317.26</v>
+        <v>133452.89</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -3662,43 +3644,43 @@
         <v>76</v>
       </c>
       <c r="B66" s="4">
-        <v>183.95</v>
+        <v>0</v>
       </c>
       <c r="C66" s="4">
-        <v>649.76</v>
+        <v>138.75</v>
       </c>
       <c r="D66" s="4">
-        <v>562.6900000000001</v>
+        <v>0</v>
       </c>
       <c r="E66" s="4">
-        <v>183.95</v>
+        <v>0</v>
       </c>
       <c r="F66" s="4">
-        <v>4284.8</v>
+        <v>1102.5</v>
       </c>
       <c r="G66" s="4">
-        <v>562.6900000000001</v>
+        <v>0</v>
       </c>
       <c r="H66" s="4">
-        <v>4014.51</v>
+        <v>0</v>
       </c>
       <c r="I66" s="4">
-        <v>866.6966666666667</v>
+        <v>0</v>
       </c>
       <c r="J66" s="4">
-        <v>3941.28</v>
+        <v>1218.75</v>
       </c>
       <c r="K66" s="4">
-        <v>3078.95</v>
+        <v>0</v>
       </c>
       <c r="L66" s="4">
-        <v>16013.32374999999</v>
+        <v>0</v>
       </c>
       <c r="M66" s="4">
-        <v>29187.84</v>
+        <v>7743.75</v>
       </c>
       <c r="N66" s="4">
-        <v>36580.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -3706,43 +3688,43 @@
         <v>77</v>
       </c>
       <c r="B67" s="5">
-        <v>12.69873047212078</v>
+        <v>0</v>
       </c>
       <c r="C67" s="5">
-        <v>16.65628468670774</v>
+        <v>3.168075842023184</v>
       </c>
       <c r="D67" s="5">
-        <v>46.35428251324255</v>
+        <v>0</v>
       </c>
       <c r="E67" s="5">
-        <v>12.69873047212078</v>
+        <v>0</v>
       </c>
       <c r="F67" s="5">
-        <v>16.49539781942606</v>
+        <v>3.341678689637614</v>
       </c>
       <c r="G67" s="5">
-        <v>46.35428251324255</v>
+        <v>0</v>
       </c>
       <c r="H67" s="5">
-        <v>29.97784430377573</v>
+        <v>0</v>
       </c>
       <c r="I67" s="5">
-        <v>3.706104669601515</v>
+        <v>0</v>
       </c>
       <c r="J67" s="5">
-        <v>12.44900408725371</v>
+        <v>3.192843838171611</v>
       </c>
       <c r="K67" s="5">
-        <v>11.44966916649592</v>
+        <v>0</v>
       </c>
       <c r="L67" s="5">
-        <v>12.3712328105686</v>
+        <v>0</v>
       </c>
       <c r="M67" s="5">
-        <v>17.54456703909103</v>
+        <v>4.202218771511358</v>
       </c>
       <c r="N67" s="5">
-        <v>19.52865422011832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -3750,43 +3732,43 @@
         <v>78</v>
       </c>
       <c r="B68" s="4">
-        <v>3921.86</v>
+        <v>0</v>
       </c>
       <c r="C68" s="4">
-        <v>4379.63</v>
+        <v>0</v>
       </c>
       <c r="D68" s="4">
-        <v>2679.72</v>
+        <v>0</v>
       </c>
       <c r="E68" s="4">
-        <v>3921.86</v>
+        <v>0</v>
       </c>
       <c r="F68" s="4">
-        <v>32992.4</v>
+        <v>0</v>
       </c>
       <c r="G68" s="4">
-        <v>2679.72</v>
+        <v>0</v>
       </c>
       <c r="H68" s="4">
-        <v>21355.43</v>
+        <v>0</v>
       </c>
       <c r="I68" s="4">
-        <v>33099.05</v>
+        <v>0</v>
       </c>
       <c r="J68" s="4">
-        <v>38171.3</v>
+        <v>0</v>
       </c>
       <c r="K68" s="4">
-        <v>30386.91</v>
+        <v>0</v>
       </c>
       <c r="L68" s="4">
-        <v>128420.01</v>
+        <v>0</v>
       </c>
       <c r="M68" s="4">
-        <v>184277.65</v>
+        <v>0</v>
       </c>
       <c r="N68" s="4">
-        <v>144373.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -3797,40 +3779,40 @@
         <v>0</v>
       </c>
       <c r="C69" s="4">
-        <v>138.75</v>
+        <v>1066.11</v>
       </c>
       <c r="D69" s="4">
-        <v>0</v>
+        <v>1553.26</v>
       </c>
       <c r="E69" s="4">
         <v>0</v>
       </c>
       <c r="F69" s="4">
-        <v>1102.5</v>
+        <v>7462.77</v>
       </c>
       <c r="G69" s="4">
-        <v>0</v>
+        <v>1553.26</v>
       </c>
       <c r="H69" s="4">
-        <v>0</v>
+        <v>11851.29</v>
       </c>
       <c r="I69" s="4">
-        <v>0</v>
+        <v>262.8222222222223</v>
       </c>
       <c r="J69" s="4">
-        <v>1218.75</v>
+        <v>5330.55</v>
       </c>
       <c r="K69" s="4">
-        <v>0</v>
+        <v>8912.91</v>
       </c>
       <c r="L69" s="4">
-        <v>0</v>
+        <v>1354.398888888889</v>
       </c>
       <c r="M69" s="4">
-        <v>7743.75</v>
+        <v>70363.25999999999</v>
       </c>
       <c r="N69" s="4">
-        <v>0</v>
+        <v>109803.41</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -3841,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="C70" s="5">
-        <v>3.168075842023184</v>
+        <v>0</v>
       </c>
       <c r="D70" s="5">
         <v>0</v>
@@ -3850,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="5">
-        <v>3.341678689637614</v>
+        <v>0</v>
       </c>
       <c r="G70" s="5">
         <v>0</v>
@@ -3862,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="5">
-        <v>3.192843838171611</v>
+        <v>0</v>
       </c>
       <c r="K70" s="5">
         <v>0</v>
@@ -3871,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="5">
-        <v>4.202218771511358</v>
+        <v>0</v>
       </c>
       <c r="N70" s="5">
         <v>0</v>
@@ -3882,43 +3864,43 @@
         <v>81</v>
       </c>
       <c r="B71" s="4">
-        <v>0</v>
+        <v>4342.26</v>
       </c>
       <c r="C71" s="4">
-        <v>0</v>
+        <v>4846.01</v>
       </c>
       <c r="D71" s="4">
-        <v>0</v>
+        <v>3831.83</v>
       </c>
       <c r="E71" s="4">
-        <v>0</v>
+        <v>4342.26</v>
       </c>
       <c r="F71" s="4">
-        <v>0</v>
+        <v>36505.66</v>
       </c>
       <c r="G71" s="4">
-        <v>0</v>
+        <v>3831.83</v>
       </c>
       <c r="H71" s="4">
-        <v>0</v>
+        <v>24527.62</v>
       </c>
       <c r="I71" s="4">
-        <v>0</v>
+        <v>33174.51</v>
       </c>
       <c r="J71" s="4">
-        <v>0</v>
+        <v>42236.05</v>
       </c>
       <c r="K71" s="4">
-        <v>0</v>
+        <v>39353.69</v>
       </c>
       <c r="L71" s="4">
-        <v>0</v>
+        <v>154034.34</v>
       </c>
       <c r="M71" s="4">
-        <v>0</v>
+        <v>203901.12</v>
       </c>
       <c r="N71" s="4">
-        <v>0</v>
+        <v>173710.76</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -3926,43 +3908,43 @@
         <v>82</v>
       </c>
       <c r="B72" s="4">
-        <v>1210.6</v>
+        <v>146.4958333333333</v>
       </c>
       <c r="C72" s="4">
-        <v>1066.11</v>
+        <v>928</v>
       </c>
       <c r="D72" s="4">
-        <v>1553.26</v>
+        <v>795.5700000000001</v>
       </c>
       <c r="E72" s="4">
-        <v>1210.6</v>
+        <v>146.4958333333333</v>
       </c>
       <c r="F72" s="4">
-        <v>7462.77</v>
+        <v>6390.74</v>
       </c>
       <c r="G72" s="4">
-        <v>1553.26</v>
+        <v>795.5700000000001</v>
       </c>
       <c r="H72" s="4">
-        <v>11851.29</v>
+        <v>6365.54</v>
       </c>
       <c r="I72" s="4">
-        <v>6315.822222222222</v>
+        <v>1584.619111111111</v>
       </c>
       <c r="J72" s="4">
-        <v>5330.55</v>
+        <v>4747.24</v>
       </c>
       <c r="K72" s="4">
-        <v>8912.91</v>
+        <v>5320.91</v>
       </c>
       <c r="L72" s="4">
-        <v>81253.99888888889</v>
+        <v>9690.84623055556</v>
       </c>
       <c r="M72" s="4">
-        <v>70363.25999999999</v>
+        <v>38003.58</v>
       </c>
       <c r="N72" s="4">
-        <v>109803.41</v>
+        <v>36897.76</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -3970,43 +3952,43 @@
         <v>83</v>
       </c>
       <c r="B73" s="5">
-        <v>0</v>
+        <v>3.373723207116416</v>
       </c>
       <c r="C73" s="5">
-        <v>0</v>
+        <v>19.14977476315567</v>
       </c>
       <c r="D73" s="5">
-        <v>0</v>
+        <v>20.76214237061665</v>
       </c>
       <c r="E73" s="5">
-        <v>0</v>
+        <v>3.373723207116416</v>
       </c>
       <c r="F73" s="5">
-        <v>0</v>
+        <v>17.50616205815755</v>
       </c>
       <c r="G73" s="5">
-        <v>0</v>
+        <v>20.76214237061665</v>
       </c>
       <c r="H73" s="5">
-        <v>0</v>
+        <v>25.95253840364454</v>
       </c>
       <c r="I73" s="5">
-        <v>0</v>
+        <v>4.776616477865417</v>
       </c>
       <c r="J73" s="5">
-        <v>0</v>
+        <v>11.23978212924741</v>
       </c>
       <c r="K73" s="5">
-        <v>0</v>
+        <v>13.52073973241137</v>
       </c>
       <c r="L73" s="5">
-        <v>0</v>
+        <v>6.291354402242747</v>
       </c>
       <c r="M73" s="5">
-        <v>0</v>
+        <v>18.63823994689191</v>
       </c>
       <c r="N73" s="5">
-        <v>0</v>
+        <v>21.2409179488939</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -4014,43 +3996,43 @@
         <v>84</v>
       </c>
       <c r="B74" s="4">
-        <v>4342.26</v>
+        <v>4223.53</v>
       </c>
       <c r="C74" s="4">
-        <v>4846.01</v>
+        <v>7047.16</v>
       </c>
       <c r="D74" s="4">
-        <v>3831.83</v>
+        <v>5201.44</v>
       </c>
       <c r="E74" s="4">
-        <v>4342.26</v>
+        <v>4223.53</v>
       </c>
       <c r="F74" s="4">
-        <v>36505.66</v>
+        <v>53087.17</v>
       </c>
       <c r="G74" s="4">
-        <v>3831.83</v>
+        <v>5201.44</v>
       </c>
       <c r="H74" s="4">
-        <v>35658.44</v>
+        <v>47408.21</v>
       </c>
       <c r="I74" s="4">
-        <v>33174.51</v>
+        <v>26140.05</v>
       </c>
       <c r="J74" s="4">
-        <v>42236.05</v>
+        <v>61420.36</v>
       </c>
       <c r="K74" s="4">
-        <v>39353.69</v>
+        <v>64219.35</v>
       </c>
       <c r="L74" s="4">
-        <v>154034.34</v>
+        <v>42078.82</v>
       </c>
       <c r="M74" s="4">
-        <v>203901.12</v>
+        <v>228435.47</v>
       </c>
       <c r="N74" s="4">
-        <v>203239.07</v>
+        <v>189607.02</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -4058,43 +4040,43 @@
         <v>85</v>
       </c>
       <c r="B75" s="4">
-        <v>839.2517666666668</v>
+        <v>174.3255555555556</v>
       </c>
       <c r="C75" s="4">
-        <v>928</v>
+        <v>2266.33</v>
       </c>
       <c r="D75" s="4">
-        <v>795.5700000000001</v>
+        <v>2968.74</v>
       </c>
       <c r="E75" s="4">
-        <v>839.2517666666668</v>
+        <v>174.3255555555556</v>
       </c>
       <c r="F75" s="4">
-        <v>6390.74</v>
+        <v>17513.87</v>
       </c>
       <c r="G75" s="4">
-        <v>795.5700000000001</v>
+        <v>2968.74</v>
       </c>
       <c r="H75" s="4">
-        <v>6365.54</v>
+        <v>18995.44</v>
       </c>
       <c r="I75" s="4">
-        <v>4174.48321111111</v>
+        <v>884.5527777777778</v>
       </c>
       <c r="J75" s="4">
-        <v>4747.24</v>
+        <v>13226.35</v>
       </c>
       <c r="K75" s="4">
-        <v>5320.91</v>
+        <v>14802.01</v>
       </c>
       <c r="L75" s="4">
-        <v>29231.22314166666</v>
+        <v>3041.316111111111</v>
       </c>
       <c r="M75" s="4">
-        <v>38003.58</v>
+        <v>57501.89</v>
       </c>
       <c r="N75" s="4">
-        <v>36897.76</v>
+        <v>57411.01</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -4102,43 +4084,43 @@
         <v>86</v>
       </c>
       <c r="B76" s="5">
-        <v>19.32753374202988</v>
+        <v>4.127484723810547</v>
       </c>
       <c r="C76" s="5">
-        <v>19.14977476315567</v>
+        <v>32.15947984720086</v>
       </c>
       <c r="D76" s="5">
-        <v>20.76214237061665</v>
+        <v>57.07534836506814</v>
       </c>
       <c r="E76" s="5">
-        <v>19.32753374202988</v>
+        <v>4.127484723810547</v>
       </c>
       <c r="F76" s="5">
-        <v>17.50616205815755</v>
+        <v>32.99077724429462</v>
       </c>
       <c r="G76" s="5">
-        <v>20.76214237061665</v>
+        <v>57.07534836506814</v>
       </c>
       <c r="H76" s="5">
-        <v>17.85142591767895</v>
+        <v>40.06782791419461</v>
       </c>
       <c r="I76" s="5">
-        <v>12.58340578688611</v>
+        <v>3.383898568586432</v>
       </c>
       <c r="J76" s="5">
-        <v>11.23978212924741</v>
+        <v>21.53414600630801</v>
       </c>
       <c r="K76" s="5">
-        <v>13.52073973241137</v>
+        <v>23.04914328780967</v>
       </c>
       <c r="L76" s="5">
-        <v>18.97708208550552</v>
+        <v>7.227664918149109</v>
       </c>
       <c r="M76" s="5">
-        <v>18.63823994689191</v>
+        <v>25.17204968212686</v>
       </c>
       <c r="N76" s="5">
-        <v>18.1548557568188</v>
+        <v>30.27894747778854</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -4146,43 +4128,43 @@
         <v>87</v>
       </c>
       <c r="B77" s="4">
-        <v>4223.53</v>
+        <v>0</v>
       </c>
       <c r="C77" s="4">
-        <v>7047.16</v>
+        <v>0</v>
       </c>
       <c r="D77" s="4">
-        <v>5201.44</v>
+        <v>0</v>
       </c>
       <c r="E77" s="4">
-        <v>4223.53</v>
+        <v>0</v>
       </c>
       <c r="F77" s="4">
-        <v>53087.17</v>
+        <v>0</v>
       </c>
       <c r="G77" s="4">
-        <v>5201.44</v>
+        <v>0</v>
       </c>
       <c r="H77" s="4">
-        <v>52609.65</v>
+        <v>0</v>
       </c>
       <c r="I77" s="4">
-        <v>26140.05</v>
+        <v>0</v>
       </c>
       <c r="J77" s="4">
-        <v>61420.36</v>
+        <v>0</v>
       </c>
       <c r="K77" s="4">
-        <v>64219.35</v>
+        <v>0</v>
       </c>
       <c r="L77" s="4">
-        <v>42078.82</v>
+        <v>0</v>
       </c>
       <c r="M77" s="4">
-        <v>228435.47</v>
+        <v>0</v>
       </c>
       <c r="N77" s="4">
-        <v>220034.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -4190,43 +4172,43 @@
         <v>88</v>
       </c>
       <c r="B78" s="4">
-        <v>1650.368827777778</v>
+        <v>0</v>
       </c>
       <c r="C78" s="4">
-        <v>2266.33</v>
+        <v>0</v>
       </c>
       <c r="D78" s="4">
-        <v>2968.74</v>
+        <v>0</v>
       </c>
       <c r="E78" s="4">
-        <v>1650.368827777778</v>
+        <v>0</v>
       </c>
       <c r="F78" s="4">
-        <v>17513.87</v>
+        <v>0</v>
       </c>
       <c r="G78" s="4">
-        <v>2968.74</v>
+        <v>0</v>
       </c>
       <c r="H78" s="4">
-        <v>18995.44</v>
+        <v>0</v>
       </c>
       <c r="I78" s="4">
-        <v>8325.156705555552</v>
+        <v>0</v>
       </c>
       <c r="J78" s="4">
-        <v>13226.35</v>
+        <v>0</v>
       </c>
       <c r="K78" s="4">
-        <v>14802.01</v>
+        <v>0</v>
       </c>
       <c r="L78" s="4">
-        <v>27466.80583333332</v>
+        <v>0</v>
       </c>
       <c r="M78" s="4">
-        <v>57501.89</v>
+        <v>0</v>
       </c>
       <c r="N78" s="4">
-        <v>57411.01</v>
+        <v>1777.14</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -4234,43 +4216,43 @@
         <v>89</v>
       </c>
       <c r="B79" s="5">
-        <v>39.07557961652405</v>
+        <v>0</v>
       </c>
       <c r="C79" s="5">
-        <v>32.15947984720086</v>
+        <v>0</v>
       </c>
       <c r="D79" s="5">
-        <v>57.07534836506814</v>
+        <v>0</v>
       </c>
       <c r="E79" s="5">
-        <v>39.07557961652405</v>
+        <v>0</v>
       </c>
       <c r="F79" s="5">
-        <v>32.99077724429462</v>
+        <v>0</v>
       </c>
       <c r="G79" s="5">
-        <v>57.07534836506814</v>
+        <v>0</v>
       </c>
       <c r="H79" s="5">
-        <v>36.10637972311163</v>
+        <v>0</v>
       </c>
       <c r="I79" s="5">
-        <v>31.84828148972765</v>
+        <v>0</v>
       </c>
       <c r="J79" s="5">
-        <v>21.53414600630801</v>
+        <v>0</v>
       </c>
       <c r="K79" s="5">
-        <v>23.04914328780967</v>
+        <v>0</v>
       </c>
       <c r="L79" s="5">
-        <v>65.27465797123904</v>
+        <v>0</v>
       </c>
       <c r="M79" s="5">
-        <v>25.17204968212686</v>
+        <v>0</v>
       </c>
       <c r="N79" s="5">
-        <v>26.09176385992065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -4278,43 +4260,43 @@
         <v>90</v>
       </c>
       <c r="B80" s="4">
-        <v>0</v>
+        <v>756.48</v>
       </c>
       <c r="C80" s="4">
-        <v>0</v>
+        <v>1035.18</v>
       </c>
       <c r="D80" s="4">
-        <v>0</v>
+        <v>534.85</v>
       </c>
       <c r="E80" s="4">
-        <v>0</v>
+        <v>756.48</v>
       </c>
       <c r="F80" s="4">
-        <v>0</v>
+        <v>7798.2</v>
       </c>
       <c r="G80" s="4">
-        <v>0</v>
+        <v>534.85</v>
       </c>
       <c r="H80" s="4">
-        <v>0</v>
+        <v>5508.59</v>
       </c>
       <c r="I80" s="4">
-        <v>0</v>
+        <v>7380.61</v>
       </c>
       <c r="J80" s="4">
-        <v>0</v>
+        <v>9022.35</v>
       </c>
       <c r="K80" s="4">
-        <v>0</v>
+        <v>8983.799999999999</v>
       </c>
       <c r="L80" s="4">
-        <v>0</v>
+        <v>24714.57</v>
       </c>
       <c r="M80" s="4">
-        <v>0</v>
+        <v>37607.32</v>
       </c>
       <c r="N80" s="4">
-        <v>0</v>
+        <v>22837.25</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -4325,40 +4307,40 @@
         <v>0</v>
       </c>
       <c r="C81" s="4">
-        <v>0</v>
+        <v>169.03</v>
       </c>
       <c r="D81" s="4">
-        <v>0</v>
+        <v>110.52</v>
       </c>
       <c r="E81" s="4">
         <v>0</v>
       </c>
       <c r="F81" s="4">
-        <v>0</v>
+        <v>1227.61</v>
       </c>
       <c r="G81" s="4">
-        <v>0</v>
+        <v>110.52</v>
       </c>
       <c r="H81" s="4">
-        <v>0</v>
+        <v>1376.54</v>
       </c>
       <c r="I81" s="4">
-        <v>0</v>
+        <v>199.472</v>
       </c>
       <c r="J81" s="4">
-        <v>0</v>
+        <v>1131.95</v>
       </c>
       <c r="K81" s="4">
-        <v>0</v>
+        <v>906.7</v>
       </c>
       <c r="L81" s="4">
-        <v>0</v>
+        <v>591.6668333333332</v>
       </c>
       <c r="M81" s="4">
-        <v>0</v>
+        <v>9557.18</v>
       </c>
       <c r="N81" s="4">
-        <v>1777.14</v>
+        <v>4504.75</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -4369,40 +4351,40 @@
         <v>0</v>
       </c>
       <c r="C82" s="5">
-        <v>0</v>
+        <v>16.32856121640681</v>
       </c>
       <c r="D82" s="5">
-        <v>0</v>
+        <v>20.66373749649434</v>
       </c>
       <c r="E82" s="5">
         <v>0</v>
       </c>
       <c r="F82" s="5">
-        <v>0</v>
+        <v>15.74222256418148</v>
       </c>
       <c r="G82" s="5">
-        <v>0</v>
+        <v>20.66373749649434</v>
       </c>
       <c r="H82" s="5">
-        <v>0</v>
+        <v>24.98897176954538</v>
       </c>
       <c r="I82" s="5">
-        <v>0</v>
+        <v>2.702649239019539</v>
       </c>
       <c r="J82" s="5">
-        <v>0</v>
+        <v>12.54606615793003</v>
       </c>
       <c r="K82" s="5">
-        <v>0</v>
+        <v>10.09261114450455</v>
       </c>
       <c r="L82" s="5">
-        <v>0</v>
+        <v>2.394000111405269</v>
       </c>
       <c r="M82" s="5">
-        <v>0</v>
+        <v>25.41308447398007</v>
       </c>
       <c r="N82" s="5">
-        <v>0</v>
+        <v>19.72544855444504</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -4410,43 +4392,43 @@
         <v>93</v>
       </c>
       <c r="B83" s="4">
-        <v>756.48</v>
+        <v>753</v>
       </c>
       <c r="C83" s="4">
-        <v>1035.18</v>
+        <v>1100.65</v>
       </c>
       <c r="D83" s="4">
-        <v>534.85</v>
+        <v>300</v>
       </c>
       <c r="E83" s="4">
-        <v>756.48</v>
+        <v>753</v>
       </c>
       <c r="F83" s="4">
-        <v>7798.2</v>
+        <v>6758.17</v>
       </c>
       <c r="G83" s="4">
-        <v>534.85</v>
+        <v>300</v>
       </c>
       <c r="H83" s="4">
-        <v>6043.44</v>
+        <v>1200</v>
       </c>
       <c r="I83" s="4">
-        <v>7380.61</v>
+        <v>3818</v>
       </c>
       <c r="J83" s="4">
-        <v>9022.35</v>
+        <v>10943.15</v>
       </c>
       <c r="K83" s="4">
-        <v>8983.799999999999</v>
+        <v>3800</v>
       </c>
       <c r="L83" s="4">
-        <v>24714.57</v>
+        <v>19414.09</v>
       </c>
       <c r="M83" s="4">
-        <v>37607.32</v>
+        <v>57336.23</v>
       </c>
       <c r="N83" s="4">
-        <v>25782.5</v>
+        <v>23247.2</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -4454,43 +4436,43 @@
         <v>94</v>
       </c>
       <c r="B84" s="4">
-        <v>265.6453111111111</v>
+        <v>245.6222222222222</v>
       </c>
       <c r="C84" s="4">
-        <v>169.03</v>
+        <v>393.9</v>
       </c>
       <c r="D84" s="4">
-        <v>110.52</v>
+        <v>583.9</v>
       </c>
       <c r="E84" s="4">
-        <v>265.6453111111111</v>
+        <v>245.6222222222222</v>
       </c>
       <c r="F84" s="4">
-        <v>1227.61</v>
+        <v>3781.3</v>
       </c>
       <c r="G84" s="4">
-        <v>110.52</v>
+        <v>583.9</v>
       </c>
       <c r="H84" s="4">
-        <v>1376.54</v>
+        <v>4847.04</v>
       </c>
       <c r="I84" s="4">
-        <v>1490.493388888889</v>
+        <v>372.75</v>
       </c>
       <c r="J84" s="4">
-        <v>1131.95</v>
+        <v>2641.5</v>
       </c>
       <c r="K84" s="4">
-        <v>906.7</v>
+        <v>3020.96</v>
       </c>
       <c r="L84" s="4">
-        <v>5176.631966666667</v>
+        <v>9499.437777777779</v>
       </c>
       <c r="M84" s="4">
-        <v>9557.18</v>
+        <v>26785.32</v>
       </c>
       <c r="N84" s="4">
-        <v>4504.75</v>
+        <v>23099.24</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -4498,43 +4480,43 @@
         <v>95</v>
       </c>
       <c r="B85" s="5">
-        <v>35.11597280973868</v>
+        <v>32.61915301755939</v>
       </c>
       <c r="C85" s="5">
-        <v>16.32856121640681</v>
+        <v>35.78794348793894</v>
       </c>
       <c r="D85" s="5">
-        <v>20.66373749649434</v>
+        <v>194.6333333333333</v>
       </c>
       <c r="E85" s="5">
-        <v>35.11597280973868</v>
+        <v>32.61915301755939</v>
       </c>
       <c r="F85" s="5">
-        <v>15.74222256418148</v>
+        <v>55.95153717648417</v>
       </c>
       <c r="G85" s="5">
-        <v>20.66373749649434</v>
+        <v>194.6333333333333</v>
       </c>
       <c r="H85" s="5">
-        <v>22.77742477794104</v>
+        <v>403.92</v>
       </c>
       <c r="I85" s="5">
-        <v>20.19471817219565</v>
+        <v>9.762964903090623</v>
       </c>
       <c r="J85" s="5">
-        <v>12.54606615793003</v>
+        <v>24.13838794131489</v>
       </c>
       <c r="K85" s="5">
-        <v>10.09261114450455</v>
+        <v>79.49894736842106</v>
       </c>
       <c r="L85" s="5">
-        <v>20.94566875598753</v>
+        <v>48.93063634596203</v>
       </c>
       <c r="M85" s="5">
-        <v>25.41308447398007</v>
+        <v>46.71622113975753</v>
       </c>
       <c r="N85" s="5">
-        <v>17.47212256375449</v>
+        <v>99.36353625382843</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -4542,43 +4524,43 @@
         <v>96</v>
       </c>
       <c r="B86" s="4">
-        <v>753</v>
+        <v>5445.72</v>
       </c>
       <c r="C86" s="4">
-        <v>1100.65</v>
+        <v>4519.34</v>
       </c>
       <c r="D86" s="4">
-        <v>300</v>
+        <v>3627.82</v>
       </c>
       <c r="E86" s="4">
-        <v>753</v>
+        <v>5445.72</v>
       </c>
       <c r="F86" s="4">
-        <v>6758.17</v>
+        <v>34044.82</v>
       </c>
       <c r="G86" s="4">
-        <v>300</v>
+        <v>3627.82</v>
       </c>
       <c r="H86" s="4">
-        <v>1500</v>
+        <v>27582.45</v>
       </c>
       <c r="I86" s="4">
-        <v>3818</v>
+        <v>32401.89</v>
       </c>
       <c r="J86" s="4">
-        <v>10943.15</v>
+        <v>39388.92</v>
       </c>
       <c r="K86" s="4">
-        <v>3811.44</v>
+        <v>35473.99</v>
       </c>
       <c r="L86" s="4">
-        <v>19414.09</v>
+        <v>118355.84</v>
       </c>
       <c r="M86" s="4">
-        <v>57336.23</v>
+        <v>164885.27</v>
       </c>
       <c r="N86" s="4">
-        <v>47501.04</v>
+        <v>102697.36</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -4586,43 +4568,43 @@
         <v>97</v>
       </c>
       <c r="B87" s="4">
-        <v>631.0155555555556</v>
+        <v>270.6757888888889</v>
       </c>
       <c r="C87" s="4">
-        <v>393.9</v>
+        <v>1169.78</v>
       </c>
       <c r="D87" s="4">
-        <v>583.9</v>
+        <v>1831.36</v>
       </c>
       <c r="E87" s="4">
-        <v>631.0155555555556</v>
+        <v>270.6757888888889</v>
       </c>
       <c r="F87" s="4">
-        <v>3781.3</v>
+        <v>9542.91</v>
       </c>
       <c r="G87" s="4">
-        <v>583.9</v>
+        <v>1831.36</v>
       </c>
       <c r="H87" s="4">
-        <v>4847.04</v>
+        <v>13109.95</v>
       </c>
       <c r="I87" s="4">
-        <v>4051.708222222222</v>
+        <v>1221.784811111111</v>
       </c>
       <c r="J87" s="4">
-        <v>2641.5</v>
+        <v>7160.7</v>
       </c>
       <c r="K87" s="4">
-        <v>3020.96</v>
+        <v>11115.51</v>
       </c>
       <c r="L87" s="4">
-        <v>39085.79352777777</v>
+        <v>7224.6225</v>
       </c>
       <c r="M87" s="4">
-        <v>26785.32</v>
+        <v>50427.23</v>
       </c>
       <c r="N87" s="4">
-        <v>23099.24</v>
+        <v>47854</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -4630,43 +4612,43 @@
         <v>98</v>
       </c>
       <c r="B88" s="5">
-        <v>83.80020658108307</v>
+        <v>4.970431621326269</v>
       </c>
       <c r="C88" s="5">
-        <v>35.78794348793894</v>
+        <v>25.88386799842455</v>
       </c>
       <c r="D88" s="5">
-        <v>194.6333333333333</v>
+        <v>50.48100512153304</v>
       </c>
       <c r="E88" s="5">
-        <v>83.80020658108307</v>
+        <v>4.970431621326269</v>
       </c>
       <c r="F88" s="5">
-        <v>55.95153717648417</v>
+        <v>28.0304316486326</v>
       </c>
       <c r="G88" s="5">
-        <v>194.6333333333333</v>
+        <v>50.48100512153304</v>
       </c>
       <c r="H88" s="5">
-        <v>323.136</v>
+        <v>47.5300417475605</v>
       </c>
       <c r="I88" s="5">
-        <v>106.1212211163494</v>
+        <v>3.770720816320008</v>
       </c>
       <c r="J88" s="5">
-        <v>24.13838794131489</v>
+        <v>18.17947788362819</v>
       </c>
       <c r="K88" s="5">
-        <v>79.26033205297736</v>
+        <v>31.3342536320273</v>
       </c>
       <c r="L88" s="5">
-        <v>201.32694104013</v>
+        <v>6.104153795875219</v>
       </c>
       <c r="M88" s="5">
-        <v>46.71622113975753</v>
+        <v>30.58322311022689</v>
       </c>
       <c r="N88" s="5">
-        <v>48.62891423008844</v>
+        <v>46.59710824114661</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -4674,43 +4656,43 @@
         <v>99</v>
       </c>
       <c r="B89" s="4">
-        <v>5445.72</v>
+        <v>12333.99</v>
       </c>
       <c r="C89" s="4">
-        <v>4519.34</v>
+        <v>13490.11</v>
       </c>
       <c r="D89" s="4">
-        <v>3627.82</v>
+        <v>13213.93</v>
       </c>
       <c r="E89" s="4">
-        <v>5445.72</v>
+        <v>12333.99</v>
       </c>
       <c r="F89" s="4">
-        <v>34044.82</v>
+        <v>101622.87</v>
       </c>
       <c r="G89" s="4">
-        <v>3627.82</v>
+        <v>13213.93</v>
       </c>
       <c r="H89" s="4">
-        <v>31210.27</v>
+        <v>84142.10000000001</v>
       </c>
       <c r="I89" s="4">
-        <v>32401.89</v>
+        <v>82324.72</v>
       </c>
       <c r="J89" s="4">
-        <v>39388.92</v>
+        <v>117574.79</v>
       </c>
       <c r="K89" s="4">
-        <v>35473.99</v>
+        <v>94771.32000000001</v>
       </c>
       <c r="L89" s="4">
-        <v>118355.84</v>
+        <v>404301.56</v>
       </c>
       <c r="M89" s="4">
-        <v>164885.27</v>
+        <v>631354.96</v>
       </c>
       <c r="N89" s="4">
-        <v>123037.64</v>
+        <v>520135.87</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -4718,43 +4700,43 @@
         <v>100</v>
       </c>
       <c r="B90" s="4">
-        <v>1669.837722222223</v>
+        <v>417.2711111111112</v>
       </c>
       <c r="C90" s="4">
-        <v>1169.78</v>
+        <v>2797.1</v>
       </c>
       <c r="D90" s="4">
-        <v>1831.36</v>
+        <v>2628.94</v>
       </c>
       <c r="E90" s="4">
-        <v>1669.837722222222</v>
+        <v>417.2711111111112</v>
       </c>
       <c r="F90" s="4">
-        <v>9542.91</v>
+        <v>20377.3</v>
       </c>
       <c r="G90" s="4">
-        <v>1831.36</v>
+        <v>2628.94</v>
       </c>
       <c r="H90" s="4">
-        <v>13109.95</v>
+        <v>17186.04</v>
       </c>
       <c r="I90" s="4">
-        <v>8735.003744444444</v>
+        <v>3072.702763888889</v>
       </c>
       <c r="J90" s="4">
-        <v>7160.7</v>
+        <v>17849.1</v>
       </c>
       <c r="K90" s="4">
-        <v>11115.51</v>
+        <v>16156.39</v>
       </c>
       <c r="L90" s="4">
-        <v>52349.45535</v>
+        <v>17056.00653055555</v>
       </c>
       <c r="M90" s="4">
-        <v>50427.23</v>
+        <v>124330.52</v>
       </c>
       <c r="N90" s="4">
-        <v>47854</v>
+        <v>108329.16</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -4762,43 +4744,43 @@
         <v>101</v>
       </c>
       <c r="B91" s="5">
-        <v>30.66330480124249</v>
+        <v>3.383099152108208</v>
       </c>
       <c r="C91" s="5">
-        <v>25.88386799842455</v>
+        <v>20.73444916312765</v>
       </c>
       <c r="D91" s="5">
-        <v>50.48100512153304</v>
+        <v>19.89521663880465</v>
       </c>
       <c r="E91" s="5">
-        <v>30.66330480124249</v>
+        <v>3.383099152108208</v>
       </c>
       <c r="F91" s="5">
-        <v>28.0304316486326</v>
+        <v>20.05188399028683</v>
       </c>
       <c r="G91" s="5">
-        <v>50.48100512153304</v>
+        <v>19.89521663880465</v>
       </c>
       <c r="H91" s="5">
-        <v>42.00524378674071</v>
+        <v>20.42501910458617</v>
       </c>
       <c r="I91" s="5">
-        <v>26.95831553173116</v>
+        <v>3.732418116804877</v>
       </c>
       <c r="J91" s="5">
-        <v>18.17947788362819</v>
+        <v>15.18106049774786</v>
       </c>
       <c r="K91" s="5">
-        <v>31.3342536320273</v>
+        <v>17.04776297301757</v>
       </c>
       <c r="L91" s="5">
-        <v>44.2305638234666</v>
+        <v>4.218634855268812</v>
       </c>
       <c r="M91" s="5">
-        <v>30.58322311022689</v>
+        <v>19.69264959920486</v>
       </c>
       <c r="N91" s="5">
-        <v>38.89378892508017</v>
+        <v>20.82708889121606</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -4806,43 +4788,43 @@
         <v>102</v>
       </c>
       <c r="B92" s="4">
-        <v>12333.99</v>
+        <v>2612.31</v>
       </c>
       <c r="C92" s="4">
-        <v>13490.11</v>
+        <v>2298.88</v>
       </c>
       <c r="D92" s="4">
-        <v>13213.93</v>
+        <v>1866.38</v>
       </c>
       <c r="E92" s="4">
-        <v>12333.99</v>
+        <v>2612.31</v>
       </c>
       <c r="F92" s="4">
-        <v>101622.87</v>
+        <v>17317.81</v>
       </c>
       <c r="G92" s="4">
-        <v>13213.93</v>
+        <v>1866.38</v>
       </c>
       <c r="H92" s="4">
-        <v>97356.03</v>
+        <v>12699.92</v>
       </c>
       <c r="I92" s="4">
-        <v>82324.72</v>
+        <v>19690.3</v>
       </c>
       <c r="J92" s="4">
-        <v>117574.79</v>
+        <v>20036.25</v>
       </c>
       <c r="K92" s="4">
-        <v>94771.32000000001</v>
+        <v>22210.97</v>
       </c>
       <c r="L92" s="4">
-        <v>404301.56</v>
+        <v>104341.07</v>
       </c>
       <c r="M92" s="4">
-        <v>631354.96</v>
+        <v>101182.86</v>
       </c>
       <c r="N92" s="4">
-        <v>620470.55</v>
+        <v>72679.66</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -4850,43 +4832,43 @@
         <v>103</v>
       </c>
       <c r="B93" s="4">
-        <v>2161.431744444444</v>
+        <v>124.0256444444444</v>
       </c>
       <c r="C93" s="4">
-        <v>2797.1</v>
+        <v>321.5</v>
       </c>
       <c r="D93" s="4">
-        <v>2628.94</v>
+        <v>464.54</v>
       </c>
       <c r="E93" s="4">
-        <v>2161.431744444444</v>
+        <v>124.0256444444444</v>
       </c>
       <c r="F93" s="4">
-        <v>20377.3</v>
+        <v>2499.65</v>
       </c>
       <c r="G93" s="4">
-        <v>2628.94</v>
+        <v>464.54</v>
       </c>
       <c r="H93" s="4">
-        <v>17186.04</v>
+        <v>3009.84</v>
       </c>
       <c r="I93" s="4">
-        <v>13245.30865833334</v>
+        <v>124.0256444444444</v>
       </c>
       <c r="J93" s="4">
-        <v>17849.1</v>
+        <v>1965.6</v>
       </c>
       <c r="K93" s="4">
-        <v>16156.39</v>
+        <v>2001.28</v>
       </c>
       <c r="L93" s="4">
-        <v>100259.4549083334</v>
+        <v>576.8153222222221</v>
       </c>
       <c r="M93" s="4">
-        <v>124330.52</v>
+        <v>18467.5</v>
       </c>
       <c r="N93" s="4">
-        <v>108329.16</v>
+        <v>14123.31</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -4894,43 +4876,43 @@
         <v>104</v>
       </c>
       <c r="B94" s="5">
-        <v>17.52418920758363</v>
+        <v>4.747738378846479</v>
       </c>
       <c r="C94" s="5">
-        <v>20.73444916312765</v>
+        <v>13.98507099109131</v>
       </c>
       <c r="D94" s="5">
-        <v>19.89521663880465</v>
+        <v>24.88989380512007</v>
       </c>
       <c r="E94" s="5">
-        <v>17.52418920758363</v>
+        <v>4.747738378846479</v>
       </c>
       <c r="F94" s="5">
-        <v>20.05188399028683</v>
+        <v>14.43398443567633</v>
       </c>
       <c r="G94" s="5">
-        <v>19.89521663880465</v>
+        <v>24.88989380512007</v>
       </c>
       <c r="H94" s="5">
-        <v>17.65277405005114</v>
+        <v>23.6996768483581</v>
       </c>
       <c r="I94" s="5">
-        <v>16.08910259073257</v>
+        <v>0.6298819441270292</v>
       </c>
       <c r="J94" s="5">
-        <v>15.18106049774786</v>
+        <v>9.810218978102188</v>
       </c>
       <c r="K94" s="5">
-        <v>17.04776297301757</v>
+        <v>9.010322376735459</v>
       </c>
       <c r="L94" s="5">
-        <v>24.79818650918226</v>
+        <v>0.5528171430695717</v>
       </c>
       <c r="M94" s="5">
-        <v>19.69264959920486</v>
+        <v>18.25160901757472</v>
       </c>
       <c r="N94" s="5">
-        <v>17.45919447748165</v>
+        <v>19.43227307337431</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -4938,43 +4920,43 @@
         <v>105</v>
       </c>
       <c r="B95" s="4">
-        <v>2612.31</v>
+        <v>0</v>
       </c>
       <c r="C95" s="4">
-        <v>2298.88</v>
+        <v>0</v>
       </c>
       <c r="D95" s="4">
-        <v>1866.38</v>
+        <v>0</v>
       </c>
       <c r="E95" s="4">
-        <v>2612.31</v>
+        <v>0</v>
       </c>
       <c r="F95" s="4">
-        <v>17317.81</v>
+        <v>0</v>
       </c>
       <c r="G95" s="4">
-        <v>1866.38</v>
+        <v>0</v>
       </c>
       <c r="H95" s="4">
-        <v>14566.3</v>
+        <v>1060</v>
       </c>
       <c r="I95" s="4">
-        <v>19690.3</v>
+        <v>0</v>
       </c>
       <c r="J95" s="4">
-        <v>20036.25</v>
+        <v>0</v>
       </c>
       <c r="K95" s="4">
-        <v>22210.97</v>
+        <v>12000</v>
       </c>
       <c r="L95" s="4">
-        <v>104341.07</v>
+        <v>804.4400000000001</v>
       </c>
       <c r="M95" s="4">
-        <v>101182.86</v>
+        <v>43000</v>
       </c>
       <c r="N95" s="4">
-        <v>92274.42999999999</v>
+        <v>48830</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -4982,43 +4964,43 @@
         <v>106</v>
       </c>
       <c r="B96" s="4">
-        <v>362.5429777777778</v>
+        <v>0</v>
       </c>
       <c r="C96" s="4">
-        <v>321.5</v>
+        <v>201.25</v>
       </c>
       <c r="D96" s="4">
-        <v>464.54</v>
+        <v>195.88</v>
       </c>
       <c r="E96" s="4">
-        <v>362.5429777777778</v>
+        <v>0</v>
       </c>
       <c r="F96" s="4">
-        <v>2499.65</v>
+        <v>1408.75</v>
       </c>
       <c r="G96" s="4">
-        <v>464.54</v>
+        <v>195.88</v>
       </c>
       <c r="H96" s="4">
-        <v>3009.84</v>
+        <v>1597.96</v>
       </c>
       <c r="I96" s="4">
-        <v>1377.9303</v>
+        <v>0</v>
       </c>
       <c r="J96" s="4">
-        <v>1965.6</v>
+        <v>1006.25</v>
       </c>
       <c r="K96" s="4">
-        <v>2001.28</v>
+        <v>979.4</v>
       </c>
       <c r="L96" s="4">
-        <v>11659.1017388889</v>
+        <v>0</v>
       </c>
       <c r="M96" s="4">
-        <v>18467.5</v>
+        <v>13282.5</v>
       </c>
       <c r="N96" s="4">
-        <v>14123.31</v>
+        <v>13129.38</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -5026,43 +5008,43 @@
         <v>107</v>
       </c>
       <c r="B97" s="5">
-        <v>13.87825249598163</v>
+        <v>0</v>
       </c>
       <c r="C97" s="5">
-        <v>13.98507099109131</v>
+        <v>0</v>
       </c>
       <c r="D97" s="5">
-        <v>24.88989380512007</v>
+        <v>0</v>
       </c>
       <c r="E97" s="5">
-        <v>13.87825249598163</v>
+        <v>0</v>
       </c>
       <c r="F97" s="5">
-        <v>14.43398443567633</v>
+        <v>0</v>
       </c>
       <c r="G97" s="5">
-        <v>24.88989380512007</v>
+        <v>0</v>
       </c>
       <c r="H97" s="5">
-        <v>20.66303728469138</v>
+        <v>150.7509433962264</v>
       </c>
       <c r="I97" s="5">
-        <v>6.998015774264485</v>
+        <v>0</v>
       </c>
       <c r="J97" s="5">
-        <v>9.810218978102188</v>
+        <v>0</v>
       </c>
       <c r="K97" s="5">
-        <v>9.010322376735459</v>
+        <v>8.161666666666667</v>
       </c>
       <c r="L97" s="5">
-        <v>11.1740293049409</v>
+        <v>0</v>
       </c>
       <c r="M97" s="5">
-        <v>18.25160901757472</v>
+        <v>30.88953488372093</v>
       </c>
       <c r="N97" s="5">
-        <v>15.30576780588079</v>
+        <v>26.88793774319066</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -5088,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="4">
-        <v>1060</v>
+        <v>0</v>
       </c>
       <c r="I98" s="4">
         <v>0</v>
@@ -5097,16 +5079,16 @@
         <v>0</v>
       </c>
       <c r="K98" s="4">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="L98" s="4">
-        <v>804.4400000000001</v>
+        <v>0</v>
       </c>
       <c r="M98" s="4">
-        <v>43000</v>
+        <v>0</v>
       </c>
       <c r="N98" s="4">
-        <v>48830</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -5114,43 +5096,43 @@
         <v>109</v>
       </c>
       <c r="B99" s="4">
-        <v>201.2</v>
+        <v>0</v>
       </c>
       <c r="C99" s="4">
-        <v>201.25</v>
+        <v>594.37</v>
       </c>
       <c r="D99" s="4">
-        <v>195.88</v>
+        <v>578.51</v>
       </c>
       <c r="E99" s="4">
-        <v>201.2</v>
+        <v>0</v>
       </c>
       <c r="F99" s="4">
-        <v>1408.75</v>
+        <v>4160.59</v>
       </c>
       <c r="G99" s="4">
-        <v>195.88</v>
+        <v>578.51</v>
       </c>
       <c r="H99" s="4">
-        <v>1597.96</v>
+        <v>4049.57</v>
       </c>
       <c r="I99" s="4">
-        <v>1006</v>
+        <v>0</v>
       </c>
       <c r="J99" s="4">
-        <v>1006.25</v>
+        <v>2971.85</v>
       </c>
       <c r="K99" s="4">
-        <v>979.4</v>
+        <v>2892.55</v>
       </c>
       <c r="L99" s="4">
-        <v>13279.2</v>
+        <v>0</v>
       </c>
       <c r="M99" s="4">
-        <v>13282.5</v>
+        <v>39228.42</v>
       </c>
       <c r="N99" s="4">
-        <v>13129.38</v>
+        <v>38181.66</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -5176,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="H100" s="5">
-        <v>150.7509433962264</v>
+        <v>0</v>
       </c>
       <c r="I100" s="5">
         <v>0</v>
@@ -5185,16 +5167,16 @@
         <v>0</v>
       </c>
       <c r="K100" s="5">
-        <v>8.161666666666667</v>
+        <v>0</v>
       </c>
       <c r="L100" s="5">
-        <v>1650.738401869624</v>
+        <v>0</v>
       </c>
       <c r="M100" s="5">
-        <v>30.88953488372093</v>
+        <v>0</v>
       </c>
       <c r="N100" s="5">
-        <v>26.88793774319066</v>
+        <v>12727.22</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -5238,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="N101" s="4">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -5246,43 +5228,43 @@
         <v>112</v>
       </c>
       <c r="B102" s="4">
-        <v>594.23</v>
+        <v>0</v>
       </c>
       <c r="C102" s="4">
-        <v>594.37</v>
+        <v>0</v>
       </c>
       <c r="D102" s="4">
-        <v>578.51</v>
+        <v>0</v>
       </c>
       <c r="E102" s="4">
-        <v>594.23</v>
+        <v>0</v>
       </c>
       <c r="F102" s="4">
-        <v>4160.59</v>
+        <v>0</v>
       </c>
       <c r="G102" s="4">
-        <v>578.51</v>
+        <v>0</v>
       </c>
       <c r="H102" s="4">
-        <v>4049.57</v>
+        <v>0</v>
       </c>
       <c r="I102" s="4">
-        <v>2971.15</v>
+        <v>0</v>
       </c>
       <c r="J102" s="4">
-        <v>2971.85</v>
+        <v>0</v>
       </c>
       <c r="K102" s="4">
-        <v>2892.55</v>
+        <v>0</v>
       </c>
       <c r="L102" s="4">
-        <v>40604.223</v>
+        <v>0</v>
       </c>
       <c r="M102" s="4">
-        <v>39228.42</v>
+        <v>0</v>
       </c>
       <c r="N102" s="4">
-        <v>38181.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -5326,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="N103" s="5">
-        <v>12727.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -5408,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="L105" s="4">
-        <v>62.8375</v>
+        <v>0</v>
       </c>
       <c r="M105" s="4">
         <v>0</v>
@@ -5469,40 +5451,40 @@
         <v>0</v>
       </c>
       <c r="C107" s="4">
-        <v>0</v>
+        <v>33687.3</v>
       </c>
       <c r="D107" s="4">
-        <v>0</v>
+        <v>18593.12</v>
       </c>
       <c r="E107" s="4">
         <v>0</v>
       </c>
       <c r="F107" s="4">
-        <v>0</v>
+        <v>375076.89</v>
       </c>
       <c r="G107" s="4">
-        <v>0</v>
+        <v>18593.12</v>
       </c>
       <c r="H107" s="4">
-        <v>0</v>
+        <v>292245.28</v>
       </c>
       <c r="I107" s="4">
         <v>0</v>
       </c>
       <c r="J107" s="4">
-        <v>0</v>
+        <v>463374.1</v>
       </c>
       <c r="K107" s="4">
-        <v>0</v>
+        <v>345018.61</v>
       </c>
       <c r="L107" s="4">
-        <v>0</v>
+        <v>620.78</v>
       </c>
       <c r="M107" s="4">
-        <v>0</v>
+        <v>1955195.62</v>
       </c>
       <c r="N107" s="4">
-        <v>0</v>
+        <v>1587998.16</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -5510,43 +5492,43 @@
         <v>118</v>
       </c>
       <c r="B108" s="4">
-        <v>0</v>
+        <v>48.84444444444444</v>
       </c>
       <c r="C108" s="4">
-        <v>0</v>
+        <v>1714</v>
       </c>
       <c r="D108" s="4">
-        <v>0</v>
+        <v>1912.3</v>
       </c>
       <c r="E108" s="4">
-        <v>0</v>
+        <v>48.84444444444444</v>
       </c>
       <c r="F108" s="4">
-        <v>0</v>
+        <v>11965.22</v>
       </c>
       <c r="G108" s="4">
-        <v>0</v>
+        <v>1912.3</v>
       </c>
       <c r="H108" s="4">
-        <v>0</v>
+        <v>14731.36</v>
       </c>
       <c r="I108" s="4">
-        <v>83.14458333333333</v>
+        <v>100.9111111111111</v>
       </c>
       <c r="J108" s="4">
-        <v>0</v>
+        <v>8822.58</v>
       </c>
       <c r="K108" s="4">
-        <v>0</v>
+        <v>9941.700000000001</v>
       </c>
       <c r="L108" s="4">
-        <v>676.4372222222222</v>
+        <v>938.8533333333335</v>
       </c>
       <c r="M108" s="4">
-        <v>0</v>
+        <v>102656.9</v>
       </c>
       <c r="N108" s="4">
-        <v>0</v>
+        <v>114482.74</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -5557,40 +5539,40 @@
         <v>0</v>
       </c>
       <c r="C109" s="5">
-        <v>0</v>
+        <v>5.087970837674732</v>
       </c>
       <c r="D109" s="5">
-        <v>0</v>
+        <v>10.28498713502629</v>
       </c>
       <c r="E109" s="5">
         <v>0</v>
       </c>
       <c r="F109" s="5">
-        <v>0</v>
+        <v>3.190071241126052</v>
       </c>
       <c r="G109" s="5">
-        <v>0</v>
+        <v>10.28498713502629</v>
       </c>
       <c r="H109" s="5">
-        <v>0</v>
+        <v>5.040752069631373</v>
       </c>
       <c r="I109" s="5">
         <v>0</v>
       </c>
       <c r="J109" s="5">
-        <v>0</v>
+        <v>1.903986433423879</v>
       </c>
       <c r="K109" s="5">
-        <v>0</v>
+        <v>2.881496740132366</v>
       </c>
       <c r="L109" s="5">
-        <v>0</v>
+        <v>151.2376902176832</v>
       </c>
       <c r="M109" s="5">
-        <v>0</v>
+        <v>5.250466958390588</v>
       </c>
       <c r="N109" s="5">
-        <v>0</v>
+        <v>7.209248907442059</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -5601,40 +5583,40 @@
         <v>0</v>
       </c>
       <c r="C110" s="4">
-        <v>33687.3</v>
+        <v>0</v>
       </c>
       <c r="D110" s="4">
-        <v>18593.12</v>
+        <v>610</v>
       </c>
       <c r="E110" s="4">
         <v>0</v>
       </c>
       <c r="F110" s="4">
-        <v>375076.89</v>
+        <v>15000</v>
       </c>
       <c r="G110" s="4">
-        <v>18593.12</v>
+        <v>610</v>
       </c>
       <c r="H110" s="4">
-        <v>333911.99</v>
+        <v>20111</v>
       </c>
       <c r="I110" s="4">
         <v>0</v>
       </c>
       <c r="J110" s="4">
-        <v>463374.1</v>
+        <v>0</v>
       </c>
       <c r="K110" s="4">
-        <v>345018.61</v>
+        <v>5285</v>
       </c>
       <c r="L110" s="4">
-        <v>620.78</v>
+        <v>0</v>
       </c>
       <c r="M110" s="4">
-        <v>1955195.62</v>
+        <v>134000</v>
       </c>
       <c r="N110" s="4">
-        <v>1629400.07</v>
+        <v>70383.73</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -5642,43 +5624,43 @@
         <v>121</v>
       </c>
       <c r="B111" s="4">
-        <v>976.8310000000001</v>
+        <v>0</v>
       </c>
       <c r="C111" s="4">
-        <v>1714</v>
+        <v>694.73</v>
       </c>
       <c r="D111" s="4">
-        <v>1912.3</v>
+        <v>770.34</v>
       </c>
       <c r="E111" s="4">
-        <v>976.8310000000001</v>
+        <v>0</v>
       </c>
       <c r="F111" s="4">
-        <v>11965.22</v>
+        <v>4008.69</v>
       </c>
       <c r="G111" s="4">
-        <v>1912.3</v>
+        <v>770.34</v>
       </c>
       <c r="H111" s="4">
-        <v>14731.36</v>
+        <v>4585.84</v>
       </c>
       <c r="I111" s="4">
-        <v>6031.658222222222</v>
+        <v>0</v>
       </c>
       <c r="J111" s="4">
-        <v>8822.58</v>
+        <v>2761.31</v>
       </c>
       <c r="K111" s="4">
-        <v>9941.700000000001</v>
+        <v>3362.81</v>
       </c>
       <c r="L111" s="4">
-        <v>81294.15281944445</v>
+        <v>0</v>
       </c>
       <c r="M111" s="4">
-        <v>102656.9</v>
+        <v>31857.42</v>
       </c>
       <c r="N111" s="4">
-        <v>114482.74</v>
+        <v>33536.61</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -5689,40 +5671,40 @@
         <v>0</v>
       </c>
       <c r="C112" s="5">
-        <v>5.087970837674732</v>
+        <v>0</v>
       </c>
       <c r="D112" s="5">
-        <v>10.28498713502629</v>
+        <v>126.2852459016393</v>
       </c>
       <c r="E112" s="5">
         <v>0</v>
       </c>
       <c r="F112" s="5">
-        <v>3.190071241126052</v>
+        <v>26.7246</v>
       </c>
       <c r="G112" s="5">
-        <v>10.28498713502629</v>
+        <v>126.2852459016393</v>
       </c>
       <c r="H112" s="5">
-        <v>4.411749335506042</v>
+        <v>22.80264531848242</v>
       </c>
       <c r="I112" s="5">
         <v>0</v>
       </c>
       <c r="J112" s="5">
-        <v>1.903986433423879</v>
+        <v>0</v>
       </c>
       <c r="K112" s="5">
-        <v>2.881496740132366</v>
+        <v>63.62932828760643</v>
       </c>
       <c r="L112" s="5">
-        <v>13095.48516695842</v>
+        <v>0</v>
       </c>
       <c r="M112" s="5">
-        <v>5.250466958390588</v>
+        <v>23.77419402985074</v>
       </c>
       <c r="N112" s="5">
-        <v>7.026066962179522</v>
+        <v>47.648242001383</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -5733,40 +5715,40 @@
         <v>0</v>
       </c>
       <c r="C113" s="4">
-        <v>0</v>
+        <v>720.12</v>
       </c>
       <c r="D113" s="4">
-        <v>610</v>
+        <v>625.95</v>
       </c>
       <c r="E113" s="4">
         <v>0</v>
       </c>
       <c r="F113" s="4">
-        <v>15000</v>
+        <v>5040.84</v>
       </c>
       <c r="G113" s="4">
-        <v>610</v>
+        <v>625.95</v>
       </c>
       <c r="H113" s="4">
-        <v>20111</v>
+        <v>4381.65</v>
       </c>
       <c r="I113" s="4">
         <v>0</v>
       </c>
       <c r="J113" s="4">
-        <v>0</v>
+        <v>3600.6</v>
       </c>
       <c r="K113" s="4">
-        <v>5285</v>
+        <v>3129.75</v>
       </c>
       <c r="L113" s="4">
         <v>0</v>
       </c>
       <c r="M113" s="4">
-        <v>134000</v>
+        <v>47527.92</v>
       </c>
       <c r="N113" s="4">
-        <v>140223.73</v>
+        <v>77965.67999999999</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -5774,43 +5756,43 @@
         <v>124</v>
       </c>
       <c r="B114" s="4">
-        <v>507.7899388888889</v>
+        <v>0</v>
       </c>
       <c r="C114" s="4">
-        <v>694.73</v>
+        <v>495.21</v>
       </c>
       <c r="D114" s="4">
-        <v>770.34</v>
+        <v>1457.24</v>
       </c>
       <c r="E114" s="4">
-        <v>507.7899388888889</v>
+        <v>0</v>
       </c>
       <c r="F114" s="4">
-        <v>4008.69</v>
+        <v>3103.91</v>
       </c>
       <c r="G114" s="4">
-        <v>770.34</v>
+        <v>1457.24</v>
       </c>
       <c r="H114" s="4">
-        <v>4585.84</v>
+        <v>9829.040000000001</v>
       </c>
       <c r="I114" s="4">
-        <v>2998.548980555556</v>
+        <v>0</v>
       </c>
       <c r="J114" s="4">
-        <v>2761.31</v>
+        <v>2113.49</v>
       </c>
       <c r="K114" s="4">
-        <v>3362.81</v>
+        <v>6782.16</v>
       </c>
       <c r="L114" s="4">
-        <v>29060.45466666666</v>
+        <v>0</v>
       </c>
       <c r="M114" s="4">
-        <v>31857.42</v>
+        <v>29058.26</v>
       </c>
       <c r="N114" s="4">
-        <v>33536.61</v>
+        <v>99652.12</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -5821,40 +5803,40 @@
         <v>0</v>
       </c>
       <c r="C115" s="5">
-        <v>0</v>
+        <v>68.76770538243626</v>
       </c>
       <c r="D115" s="5">
-        <v>126.2852459016393</v>
+        <v>232.8045371036025</v>
       </c>
       <c r="E115" s="5">
         <v>0</v>
       </c>
       <c r="F115" s="5">
-        <v>26.7246</v>
+        <v>61.57525333079407</v>
       </c>
       <c r="G115" s="5">
-        <v>126.2852459016393</v>
+        <v>232.8045371036025</v>
       </c>
       <c r="H115" s="5">
-        <v>22.80264531848242</v>
+        <v>224.3228007713989</v>
       </c>
       <c r="I115" s="5">
         <v>0</v>
       </c>
       <c r="J115" s="5">
-        <v>0</v>
+        <v>58.69827251013719</v>
       </c>
       <c r="K115" s="5">
-        <v>63.62932828760643</v>
+        <v>216.699736400671</v>
       </c>
       <c r="L115" s="5">
         <v>0</v>
       </c>
       <c r="M115" s="5">
-        <v>23.77419402985074</v>
+        <v>61.13934714584606</v>
       </c>
       <c r="N115" s="5">
-        <v>23.91650115140996</v>
+        <v>127.8153669665935</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -5865,40 +5847,40 @@
         <v>0</v>
       </c>
       <c r="C116" s="4">
-        <v>720.12</v>
+        <v>1745.45</v>
       </c>
       <c r="D116" s="4">
-        <v>625.95</v>
+        <v>1533.34</v>
       </c>
       <c r="E116" s="4">
         <v>0</v>
       </c>
       <c r="F116" s="4">
-        <v>5040.84</v>
+        <v>12218.15</v>
       </c>
       <c r="G116" s="4">
-        <v>625.95</v>
+        <v>1533.34</v>
       </c>
       <c r="H116" s="4">
-        <v>4381.65</v>
+        <v>10733.38</v>
       </c>
       <c r="I116" s="4">
         <v>0</v>
       </c>
       <c r="J116" s="4">
-        <v>3600.6</v>
+        <v>8727.25</v>
       </c>
       <c r="K116" s="4">
-        <v>3129.75</v>
+        <v>7666.7</v>
       </c>
       <c r="L116" s="4">
         <v>0</v>
       </c>
       <c r="M116" s="4">
-        <v>47527.92</v>
+        <v>115199.7</v>
       </c>
       <c r="N116" s="4">
-        <v>86247.33</v>
+        <v>281486.03</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -5906,43 +5888,43 @@
         <v>127</v>
       </c>
       <c r="B117" s="4">
-        <v>1230.52</v>
+        <v>0</v>
       </c>
       <c r="C117" s="4">
-        <v>495.21</v>
+        <v>1190.63</v>
       </c>
       <c r="D117" s="4">
-        <v>1457.24</v>
+        <v>354.62</v>
       </c>
       <c r="E117" s="4">
-        <v>1230.52</v>
+        <v>0</v>
       </c>
       <c r="F117" s="4">
-        <v>3103.91</v>
+        <v>8334.41</v>
       </c>
       <c r="G117" s="4">
-        <v>1457.24</v>
+        <v>354.62</v>
       </c>
       <c r="H117" s="4">
-        <v>9829.040000000001</v>
+        <v>2482.34</v>
       </c>
       <c r="I117" s="4">
-        <v>6433.319633333334</v>
+        <v>0</v>
       </c>
       <c r="J117" s="4">
-        <v>2113.49</v>
+        <v>5953.15</v>
       </c>
       <c r="K117" s="4">
-        <v>6782.16</v>
+        <v>1773.1</v>
       </c>
       <c r="L117" s="4">
-        <v>89266.97902222224</v>
+        <v>0</v>
       </c>
       <c r="M117" s="4">
-        <v>29058.26</v>
+        <v>78581.58</v>
       </c>
       <c r="N117" s="4">
-        <v>99652.12</v>
+        <v>23404.92</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -5953,40 +5935,40 @@
         <v>0</v>
       </c>
       <c r="C118" s="5">
-        <v>68.76770538243626</v>
+        <v>68.21335472227793</v>
       </c>
       <c r="D118" s="5">
-        <v>232.8045371036025</v>
+        <v>23.12729075090978</v>
       </c>
       <c r="E118" s="5">
         <v>0</v>
       </c>
       <c r="F118" s="5">
-        <v>61.57525333079407</v>
+        <v>68.21335472227791</v>
       </c>
       <c r="G118" s="5">
-        <v>232.8045371036025</v>
+        <v>23.12729075090978</v>
       </c>
       <c r="H118" s="5">
-        <v>224.3228007713989</v>
+        <v>23.12729075090978</v>
       </c>
       <c r="I118" s="5">
         <v>0</v>
       </c>
       <c r="J118" s="5">
-        <v>58.69827251013719</v>
+        <v>68.21335472227791</v>
       </c>
       <c r="K118" s="5">
-        <v>216.699736400671</v>
+        <v>23.12729075090978</v>
       </c>
       <c r="L118" s="5">
         <v>0</v>
       </c>
       <c r="M118" s="5">
-        <v>61.13934714584606</v>
+        <v>68.21335472227793</v>
       </c>
       <c r="N118" s="5">
-        <v>115.5422666417615</v>
+        <v>8.314771429331678</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -5994,43 +5976,43 @@
         <v>129</v>
       </c>
       <c r="B119" s="4">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="C119" s="4">
-        <v>1745.45</v>
+        <v>1147.1</v>
       </c>
       <c r="D119" s="4">
-        <v>1533.34</v>
+        <v>0</v>
       </c>
       <c r="E119" s="4">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="F119" s="4">
-        <v>12218.15</v>
+        <v>8340.299999999999</v>
       </c>
       <c r="G119" s="4">
-        <v>1533.34</v>
+        <v>0</v>
       </c>
       <c r="H119" s="4">
-        <v>10733.38</v>
+        <v>1350</v>
       </c>
       <c r="I119" s="4">
-        <v>0</v>
+        <v>4930</v>
       </c>
       <c r="J119" s="4">
-        <v>8727.25</v>
+        <v>9791.200000000001</v>
       </c>
       <c r="K119" s="4">
-        <v>7666.7</v>
+        <v>2340</v>
       </c>
       <c r="L119" s="4">
-        <v>0</v>
+        <v>23548.25</v>
       </c>
       <c r="M119" s="4">
-        <v>115199.7</v>
+        <v>46883.7</v>
       </c>
       <c r="N119" s="4">
-        <v>428459</v>
+        <v>7661.72</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -6038,43 +6020,43 @@
         <v>130</v>
       </c>
       <c r="B120" s="4">
-        <v>368.46</v>
+        <v>0</v>
       </c>
       <c r="C120" s="4">
-        <v>1190.63</v>
+        <v>391.37</v>
       </c>
       <c r="D120" s="4">
-        <v>354.62</v>
+        <v>525.9299999999999</v>
       </c>
       <c r="E120" s="4">
-        <v>368.46</v>
+        <v>0</v>
       </c>
       <c r="F120" s="4">
-        <v>8334.41</v>
+        <v>2739.59</v>
       </c>
       <c r="G120" s="4">
-        <v>354.62</v>
+        <v>525.9299999999999</v>
       </c>
       <c r="H120" s="4">
-        <v>2482.34</v>
+        <v>3837.4</v>
       </c>
       <c r="I120" s="4">
-        <v>1842.3</v>
+        <v>0</v>
       </c>
       <c r="J120" s="4">
-        <v>5953.15</v>
+        <v>1956.85</v>
       </c>
       <c r="K120" s="4">
-        <v>1773.1</v>
+        <v>2524.09</v>
       </c>
       <c r="L120" s="4">
-        <v>24318.36</v>
+        <v>0</v>
       </c>
       <c r="M120" s="4">
-        <v>78581.58</v>
+        <v>25830.42</v>
       </c>
       <c r="N120" s="4">
-        <v>23404.92</v>
+        <v>35525.45</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -6085,40 +6067,40 @@
         <v>0</v>
       </c>
       <c r="C121" s="5">
-        <v>68.21335472227793</v>
+        <v>34.11821114113852</v>
       </c>
       <c r="D121" s="5">
-        <v>23.12729075090978</v>
+        <v>0</v>
       </c>
       <c r="E121" s="5">
         <v>0</v>
       </c>
       <c r="F121" s="5">
-        <v>68.21335472227791</v>
+        <v>32.84761939018981</v>
       </c>
       <c r="G121" s="5">
-        <v>23.12729075090978</v>
+        <v>0</v>
       </c>
       <c r="H121" s="5">
-        <v>23.12729075090978</v>
+        <v>284.2518518518518</v>
       </c>
       <c r="I121" s="5">
         <v>0</v>
       </c>
       <c r="J121" s="5">
-        <v>68.21335472227791</v>
+        <v>19.98580357872375</v>
       </c>
       <c r="K121" s="5">
-        <v>23.12729075090978</v>
+        <v>107.867094017094</v>
       </c>
       <c r="L121" s="5">
         <v>0</v>
       </c>
       <c r="M121" s="5">
-        <v>68.21335472227793</v>
+        <v>55.09467042916835</v>
       </c>
       <c r="N121" s="5">
-        <v>5.462581017086816</v>
+        <v>463.6746057021139</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -6126,43 +6108,43 @@
         <v>132</v>
       </c>
       <c r="B122" s="4">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="C122" s="4">
-        <v>1147.1</v>
+        <v>0</v>
       </c>
       <c r="D122" s="4">
         <v>0</v>
       </c>
       <c r="E122" s="4">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="F122" s="4">
-        <v>8340.299999999999</v>
+        <v>0</v>
       </c>
       <c r="G122" s="4">
         <v>0</v>
       </c>
       <c r="H122" s="4">
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="I122" s="4">
-        <v>4930</v>
+        <v>0</v>
       </c>
       <c r="J122" s="4">
-        <v>9791.200000000001</v>
+        <v>0</v>
       </c>
       <c r="K122" s="4">
-        <v>2340</v>
+        <v>0</v>
       </c>
       <c r="L122" s="4">
-        <v>23548.25</v>
+        <v>0</v>
       </c>
       <c r="M122" s="4">
-        <v>46883.7</v>
+        <v>0</v>
       </c>
       <c r="N122" s="4">
-        <v>20872.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -6170,43 +6152,43 @@
         <v>133</v>
       </c>
       <c r="B123" s="4">
-        <v>389.08</v>
+        <v>0</v>
       </c>
       <c r="C123" s="4">
-        <v>391.37</v>
+        <v>0</v>
       </c>
       <c r="D123" s="4">
-        <v>525.9299999999999</v>
+        <v>0</v>
       </c>
       <c r="E123" s="4">
-        <v>389.08</v>
+        <v>0</v>
       </c>
       <c r="F123" s="4">
-        <v>2739.59</v>
+        <v>0</v>
       </c>
       <c r="G123" s="4">
-        <v>525.9299999999999</v>
+        <v>0</v>
       </c>
       <c r="H123" s="4">
-        <v>3837.4</v>
+        <v>0</v>
       </c>
       <c r="I123" s="4">
-        <v>1945.4</v>
+        <v>0</v>
       </c>
       <c r="J123" s="4">
-        <v>1956.85</v>
+        <v>0</v>
       </c>
       <c r="K123" s="4">
-        <v>2524.09</v>
+        <v>0</v>
       </c>
       <c r="L123" s="4">
-        <v>25866.21333333333</v>
+        <v>0</v>
       </c>
       <c r="M123" s="4">
-        <v>25830.42</v>
+        <v>0</v>
       </c>
       <c r="N123" s="4">
-        <v>35525.45</v>
+        <v>1332.54</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -6214,43 +6196,43 @@
         <v>134</v>
       </c>
       <c r="B124" s="5">
-        <v>82.78297872340426</v>
+        <v>0</v>
       </c>
       <c r="C124" s="5">
-        <v>34.11821114113852</v>
+        <v>0</v>
       </c>
       <c r="D124" s="5">
         <v>0</v>
       </c>
       <c r="E124" s="5">
-        <v>82.78297872340426</v>
+        <v>0</v>
       </c>
       <c r="F124" s="5">
-        <v>32.84761939018981</v>
+        <v>0</v>
       </c>
       <c r="G124" s="5">
         <v>0</v>
       </c>
       <c r="H124" s="5">
-        <v>284.2518518518518</v>
+        <v>0</v>
       </c>
       <c r="I124" s="5">
-        <v>39.4604462474645</v>
+        <v>0</v>
       </c>
       <c r="J124" s="5">
-        <v>19.98580357872375</v>
+        <v>0</v>
       </c>
       <c r="K124" s="5">
-        <v>107.867094017094</v>
+        <v>0</v>
       </c>
       <c r="L124" s="5">
-        <v>109.843463243907</v>
+        <v>0</v>
       </c>
       <c r="M124" s="5">
-        <v>55.09467042916835</v>
+        <v>0</v>
       </c>
       <c r="N124" s="5">
-        <v>170.1983474321095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -6261,40 +6243,40 @@
         <v>0</v>
       </c>
       <c r="C125" s="4">
-        <v>0</v>
+        <v>221.25</v>
       </c>
       <c r="D125" s="4">
-        <v>0</v>
+        <v>210.96</v>
       </c>
       <c r="E125" s="4">
         <v>0</v>
       </c>
       <c r="F125" s="4">
-        <v>0</v>
+        <v>1548.75</v>
       </c>
       <c r="G125" s="4">
-        <v>0</v>
+        <v>210.96</v>
       </c>
       <c r="H125" s="4">
-        <v>0</v>
+        <v>1476.72</v>
       </c>
       <c r="I125" s="4">
         <v>0</v>
       </c>
       <c r="J125" s="4">
-        <v>0</v>
+        <v>1106.25</v>
       </c>
       <c r="K125" s="4">
-        <v>0</v>
+        <v>1054.8</v>
       </c>
       <c r="L125" s="4">
         <v>0</v>
       </c>
       <c r="M125" s="4">
-        <v>0</v>
+        <v>14602.5</v>
       </c>
       <c r="N125" s="4">
-        <v>0</v>
+        <v>38781.42</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -6305,40 +6287,40 @@
         <v>0</v>
       </c>
       <c r="C126" s="4">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="D126" s="4">
-        <v>0</v>
+        <v>167.91</v>
       </c>
       <c r="E126" s="4">
         <v>0</v>
       </c>
       <c r="F126" s="4">
-        <v>0</v>
+        <v>1322.8</v>
       </c>
       <c r="G126" s="4">
-        <v>0</v>
+        <v>167.91</v>
       </c>
       <c r="H126" s="4">
-        <v>0</v>
+        <v>934.36</v>
       </c>
       <c r="I126" s="4">
         <v>0</v>
       </c>
       <c r="J126" s="4">
-        <v>0</v>
+        <v>947.1</v>
       </c>
       <c r="K126" s="4">
-        <v>0</v>
+        <v>854.26</v>
       </c>
       <c r="L126" s="4">
-        <v>0</v>
+        <v>3617.06645</v>
       </c>
       <c r="M126" s="4">
-        <v>0</v>
+        <v>12460.9</v>
       </c>
       <c r="N126" s="4">
-        <v>1332.54</v>
+        <v>12906.89</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6349,40 +6331,40 @@
         <v>0</v>
       </c>
       <c r="C127" s="5">
-        <v>0</v>
+        <v>81.35593220338984</v>
       </c>
       <c r="D127" s="5">
-        <v>0</v>
+        <v>79.59328782707622</v>
       </c>
       <c r="E127" s="5">
         <v>0</v>
       </c>
       <c r="F127" s="5">
-        <v>0</v>
+        <v>85.41081517352703</v>
       </c>
       <c r="G127" s="5">
-        <v>0</v>
+        <v>79.59328782707622</v>
       </c>
       <c r="H127" s="5">
-        <v>0</v>
+        <v>63.27265832385286</v>
       </c>
       <c r="I127" s="5">
         <v>0</v>
       </c>
       <c r="J127" s="5">
-        <v>0</v>
+        <v>85.61355932203391</v>
       </c>
       <c r="K127" s="5">
-        <v>0</v>
+        <v>80.9878649981039</v>
       </c>
       <c r="L127" s="5">
         <v>0</v>
       </c>
       <c r="M127" s="5">
-        <v>0</v>
+        <v>85.33401814757747</v>
       </c>
       <c r="N127" s="5">
-        <v>0</v>
+        <v>33.28111760734909</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -6393,40 +6375,40 @@
         <v>0</v>
       </c>
       <c r="C128" s="4">
-        <v>221.25</v>
+        <v>1635.79</v>
       </c>
       <c r="D128" s="4">
-        <v>210.96</v>
+        <v>665.41</v>
       </c>
       <c r="E128" s="4">
         <v>0</v>
       </c>
       <c r="F128" s="4">
-        <v>1548.75</v>
+        <v>11450.53</v>
       </c>
       <c r="G128" s="4">
-        <v>210.96</v>
+        <v>665.41</v>
       </c>
       <c r="H128" s="4">
-        <v>1476.72</v>
+        <v>4657.87</v>
       </c>
       <c r="I128" s="4">
         <v>0</v>
       </c>
       <c r="J128" s="4">
-        <v>1106.25</v>
+        <v>8178.95</v>
       </c>
       <c r="K128" s="4">
-        <v>1054.8</v>
+        <v>3327.05</v>
       </c>
       <c r="L128" s="4">
         <v>0</v>
       </c>
       <c r="M128" s="4">
-        <v>14602.5</v>
+        <v>107962.14</v>
       </c>
       <c r="N128" s="4">
-        <v>58875.27</v>
+        <v>99542.2</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6437,40 +6419,40 @@
         <v>0</v>
       </c>
       <c r="C129" s="4">
-        <v>180</v>
+        <v>1280.69</v>
       </c>
       <c r="D129" s="4">
-        <v>167.91</v>
+        <v>408.88</v>
       </c>
       <c r="E129" s="4">
         <v>0</v>
       </c>
       <c r="F129" s="4">
-        <v>1322.8</v>
+        <v>7950.03</v>
       </c>
       <c r="G129" s="4">
-        <v>167.91</v>
+        <v>408.88</v>
       </c>
       <c r="H129" s="4">
-        <v>934.36</v>
+        <v>4586.44</v>
       </c>
       <c r="I129" s="4">
-        <v>630.8572222222223</v>
+        <v>0</v>
       </c>
       <c r="J129" s="4">
-        <v>947.1</v>
+        <v>5597.85</v>
       </c>
       <c r="K129" s="4">
-        <v>854.26</v>
+        <v>3813.95</v>
       </c>
       <c r="L129" s="4">
-        <v>9624.659783333331</v>
+        <v>0</v>
       </c>
       <c r="M129" s="4">
-        <v>12460.9</v>
+        <v>67595.14</v>
       </c>
       <c r="N129" s="4">
-        <v>12906.89</v>
+        <v>46614.4</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -6481,40 +6463,40 @@
         <v>0</v>
       </c>
       <c r="C130" s="5">
-        <v>81.35593220338984</v>
+        <v>78.29183452643677</v>
       </c>
       <c r="D130" s="5">
-        <v>79.59328782707622</v>
+        <v>61.44782915796277</v>
       </c>
       <c r="E130" s="5">
         <v>0</v>
       </c>
       <c r="F130" s="5">
-        <v>85.41081517352703</v>
+        <v>69.42936265832236</v>
       </c>
       <c r="G130" s="5">
-        <v>79.59328782707622</v>
+        <v>61.44782915796277</v>
       </c>
       <c r="H130" s="5">
-        <v>63.27265832385286</v>
+        <v>98.46646643208162</v>
       </c>
       <c r="I130" s="5">
         <v>0</v>
       </c>
       <c r="J130" s="5">
-        <v>85.61355932203391</v>
+        <v>68.44215944589465</v>
       </c>
       <c r="K130" s="5">
-        <v>80.9878649981039</v>
+        <v>114.6345861949775</v>
       </c>
       <c r="L130" s="5">
         <v>0</v>
       </c>
       <c r="M130" s="5">
-        <v>85.33401814757747</v>
+        <v>62.61004089026023</v>
       </c>
       <c r="N130" s="5">
-        <v>21.92243024957677</v>
+        <v>46.82878216475023</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -6525,40 +6507,40 @@
         <v>0</v>
       </c>
       <c r="C131" s="4">
-        <v>1635.79</v>
+        <v>376.71</v>
       </c>
       <c r="D131" s="4">
-        <v>665.41</v>
+        <v>448.22</v>
       </c>
       <c r="E131" s="4">
         <v>0</v>
       </c>
       <c r="F131" s="4">
-        <v>11450.53</v>
+        <v>2956.97</v>
       </c>
       <c r="G131" s="4">
-        <v>665.41</v>
+        <v>448.22</v>
       </c>
       <c r="H131" s="4">
-        <v>4657.87</v>
+        <v>2849.32</v>
       </c>
       <c r="I131" s="4">
         <v>0</v>
       </c>
       <c r="J131" s="4">
-        <v>8178.95</v>
+        <v>2523.55</v>
       </c>
       <c r="K131" s="4">
-        <v>3327.05</v>
+        <v>1952.88</v>
       </c>
       <c r="L131" s="4">
         <v>0</v>
       </c>
       <c r="M131" s="4">
-        <v>107962.14</v>
+        <v>40362.86</v>
       </c>
       <c r="N131" s="4">
-        <v>191589.64</v>
+        <v>78000.42999999999</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6566,43 +6548,43 @@
         <v>142</v>
       </c>
       <c r="B132" s="4">
-        <v>1145.591944444444</v>
+        <v>118.0833333333333</v>
       </c>
       <c r="C132" s="4">
-        <v>1280.69</v>
+        <v>1592.1</v>
       </c>
       <c r="D132" s="4">
-        <v>408.88</v>
+        <v>2484.84</v>
       </c>
       <c r="E132" s="4">
-        <v>1145.591944444444</v>
+        <v>118.0833333333333</v>
       </c>
       <c r="F132" s="4">
-        <v>7950.03</v>
+        <v>12779.7</v>
       </c>
       <c r="G132" s="4">
-        <v>408.88</v>
+        <v>2484.84</v>
       </c>
       <c r="H132" s="4">
-        <v>4586.44</v>
+        <v>15855.89</v>
       </c>
       <c r="I132" s="4">
-        <v>5515.094744444445</v>
+        <v>1464.343611111111</v>
       </c>
       <c r="J132" s="4">
-        <v>5597.85</v>
+        <v>12990.5</v>
       </c>
       <c r="K132" s="4">
-        <v>3813.95</v>
+        <v>13134.83</v>
       </c>
       <c r="L132" s="4">
-        <v>69547.71462222221</v>
+        <v>10587.70763888889</v>
       </c>
       <c r="M132" s="4">
-        <v>67595.14</v>
+        <v>88179.3</v>
       </c>
       <c r="N132" s="4">
-        <v>46614.4</v>
+        <v>92478.2</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -6613,40 +6595,40 @@
         <v>0</v>
       </c>
       <c r="C133" s="5">
-        <v>78.29183452643677</v>
+        <v>422.6327944572748</v>
       </c>
       <c r="D133" s="5">
-        <v>61.44782915796277</v>
+        <v>554.3795457587792</v>
       </c>
       <c r="E133" s="5">
         <v>0</v>
       </c>
       <c r="F133" s="5">
-        <v>69.42936265832236</v>
+        <v>432.1890313395131</v>
       </c>
       <c r="G133" s="5">
-        <v>61.44782915796277</v>
+        <v>554.3795457587792</v>
       </c>
       <c r="H133" s="5">
-        <v>98.46646643208162</v>
+        <v>556.4797916695912</v>
       </c>
       <c r="I133" s="5">
         <v>0</v>
       </c>
       <c r="J133" s="5">
-        <v>68.44215944589465</v>
+        <v>514.7708585128094</v>
       </c>
       <c r="K133" s="5">
-        <v>114.6345861949775</v>
+        <v>672.5876653967473</v>
       </c>
       <c r="L133" s="5">
         <v>0</v>
       </c>
       <c r="M133" s="5">
-        <v>62.61004089026023</v>
+        <v>218.4664317642506</v>
       </c>
       <c r="N133" s="5">
-        <v>24.33033435419577</v>
+        <v>118.5611412655033</v>
       </c>
     </row>
     <row r="134" spans="1:14">
@@ -6657,40 +6639,40 @@
         <v>0</v>
       </c>
       <c r="C134" s="4">
-        <v>376.71</v>
+        <v>0</v>
       </c>
       <c r="D134" s="4">
-        <v>448.22</v>
+        <v>0</v>
       </c>
       <c r="E134" s="4">
         <v>0</v>
       </c>
       <c r="F134" s="4">
-        <v>2956.97</v>
+        <v>0</v>
       </c>
       <c r="G134" s="4">
-        <v>448.22</v>
+        <v>0</v>
       </c>
       <c r="H134" s="4">
-        <v>3297.54</v>
+        <v>0</v>
       </c>
       <c r="I134" s="4">
         <v>0</v>
       </c>
       <c r="J134" s="4">
-        <v>2523.55</v>
+        <v>0</v>
       </c>
       <c r="K134" s="4">
-        <v>2401.1</v>
+        <v>0</v>
       </c>
       <c r="L134" s="4">
         <v>0</v>
       </c>
       <c r="M134" s="4">
-        <v>40362.86</v>
+        <v>0</v>
       </c>
       <c r="N134" s="4">
-        <v>124610.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -6698,43 +6680,43 @@
         <v>145</v>
       </c>
       <c r="B135" s="4">
-        <v>1518.115744444444</v>
+        <v>0</v>
       </c>
       <c r="C135" s="4">
-        <v>1592.1</v>
+        <v>0</v>
       </c>
       <c r="D135" s="4">
-        <v>2484.84</v>
+        <v>0</v>
       </c>
       <c r="E135" s="4">
-        <v>1518.115744444444</v>
+        <v>0</v>
       </c>
       <c r="F135" s="4">
-        <v>12779.7</v>
+        <v>0</v>
       </c>
       <c r="G135" s="4">
-        <v>2484.84</v>
+        <v>0</v>
       </c>
       <c r="H135" s="4">
-        <v>15855.89</v>
+        <v>865.13</v>
       </c>
       <c r="I135" s="4">
-        <v>10855.85846111112</v>
+        <v>0</v>
       </c>
       <c r="J135" s="4">
-        <v>12990.5</v>
+        <v>0</v>
       </c>
       <c r="K135" s="4">
-        <v>13134.83</v>
+        <v>436.25</v>
       </c>
       <c r="L135" s="4">
-        <v>74417.46996666677</v>
+        <v>0</v>
       </c>
       <c r="M135" s="4">
-        <v>88179.3</v>
+        <v>0</v>
       </c>
       <c r="N135" s="4">
-        <v>92478.2</v>
+        <v>3890.51</v>
       </c>
     </row>
     <row r="136" spans="1:14">
@@ -6745,40 +6727,40 @@
         <v>0</v>
       </c>
       <c r="C136" s="5">
-        <v>422.6327944572748</v>
+        <v>0</v>
       </c>
       <c r="D136" s="5">
-        <v>554.3795457587792</v>
+        <v>0</v>
       </c>
       <c r="E136" s="5">
         <v>0</v>
       </c>
       <c r="F136" s="5">
-        <v>432.1890313395131</v>
+        <v>0</v>
       </c>
       <c r="G136" s="5">
-        <v>554.3795457587792</v>
+        <v>0</v>
       </c>
       <c r="H136" s="5">
-        <v>480.8399594849494</v>
+        <v>0</v>
       </c>
       <c r="I136" s="5">
         <v>0</v>
       </c>
       <c r="J136" s="5">
-        <v>514.7708585128094</v>
+        <v>0</v>
       </c>
       <c r="K136" s="5">
-        <v>547.0338594810712</v>
+        <v>0</v>
       </c>
       <c r="L136" s="5">
         <v>0</v>
       </c>
       <c r="M136" s="5">
-        <v>218.4664317642506</v>
+        <v>0</v>
       </c>
       <c r="N136" s="5">
-        <v>74.21372685350143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:14">
@@ -6789,40 +6771,40 @@
         <v>0</v>
       </c>
       <c r="C137" s="4">
-        <v>0</v>
+        <v>863.28</v>
       </c>
       <c r="D137" s="4">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="E137" s="4">
         <v>0</v>
       </c>
       <c r="F137" s="4">
-        <v>0</v>
+        <v>6042.96</v>
       </c>
       <c r="G137" s="4">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="H137" s="4">
-        <v>0</v>
+        <v>2226.52</v>
       </c>
       <c r="I137" s="4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J137" s="4">
-        <v>0</v>
+        <v>4316.4</v>
       </c>
       <c r="K137" s="4">
-        <v>0</v>
+        <v>2216.52</v>
       </c>
       <c r="L137" s="4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M137" s="4">
-        <v>0</v>
+        <v>42676.48</v>
       </c>
       <c r="N137" s="4">
-        <v>0</v>
+        <v>39592.9</v>
       </c>
     </row>
     <row r="138" spans="1:14">
@@ -6833,40 +6815,40 @@
         <v>0</v>
       </c>
       <c r="C138" s="4">
-        <v>0</v>
+        <v>879</v>
       </c>
       <c r="D138" s="4">
-        <v>0</v>
+        <v>1426.42</v>
       </c>
       <c r="E138" s="4">
         <v>0</v>
       </c>
       <c r="F138" s="4">
-        <v>0</v>
+        <v>6945.5</v>
       </c>
       <c r="G138" s="4">
-        <v>0</v>
+        <v>1426.42</v>
       </c>
       <c r="H138" s="4">
-        <v>865.13</v>
+        <v>8301.610000000001</v>
       </c>
       <c r="I138" s="4">
-        <v>0</v>
+        <v>456.1620833333333</v>
       </c>
       <c r="J138" s="4">
-        <v>0</v>
+        <v>7975.25</v>
       </c>
       <c r="K138" s="4">
-        <v>436.25</v>
+        <v>10155.63</v>
       </c>
       <c r="L138" s="4">
-        <v>716.1311111111111</v>
+        <v>2822.434999999999</v>
       </c>
       <c r="M138" s="4">
-        <v>0</v>
+        <v>54095.75</v>
       </c>
       <c r="N138" s="4">
-        <v>3890.51</v>
+        <v>54810.04</v>
       </c>
     </row>
     <row r="139" spans="1:14">
@@ -6877,40 +6859,40 @@
         <v>0</v>
       </c>
       <c r="C139" s="5">
-        <v>0</v>
+        <v>101.820961912705</v>
       </c>
       <c r="D139" s="5">
-        <v>0</v>
+        <v>419.5352941176471</v>
       </c>
       <c r="E139" s="5">
         <v>0</v>
       </c>
       <c r="F139" s="5">
-        <v>0</v>
+        <v>114.9353958986987</v>
       </c>
       <c r="G139" s="5">
-        <v>0</v>
+        <v>419.5352941176471</v>
       </c>
       <c r="H139" s="5">
-        <v>0</v>
+        <v>372.8513554785046</v>
       </c>
       <c r="I139" s="5">
-        <v>0</v>
+        <v>380.1350694444444</v>
       </c>
       <c r="J139" s="5">
-        <v>0</v>
+        <v>184.7662403855065</v>
       </c>
       <c r="K139" s="5">
-        <v>0</v>
+        <v>458.179037409994</v>
       </c>
       <c r="L139" s="5">
-        <v>0</v>
+        <v>940.8116666666665</v>
       </c>
       <c r="M139" s="5">
-        <v>0</v>
+        <v>126.7577597777511</v>
       </c>
       <c r="N139" s="5">
-        <v>0</v>
+        <v>138.4340121587456</v>
       </c>
     </row>
     <row r="140" spans="1:14">
@@ -6921,40 +6903,40 @@
         <v>0</v>
       </c>
       <c r="C140" s="4">
-        <v>863.28</v>
+        <v>0</v>
       </c>
       <c r="D140" s="4">
-        <v>748.26</v>
+        <v>900</v>
       </c>
       <c r="E140" s="4">
         <v>0</v>
       </c>
       <c r="F140" s="4">
-        <v>6042.96</v>
+        <v>0</v>
       </c>
       <c r="G140" s="4">
-        <v>748.26</v>
+        <v>900</v>
       </c>
       <c r="H140" s="4">
-        <v>4267.82</v>
+        <v>4057.54</v>
       </c>
       <c r="I140" s="4">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="J140" s="4">
-        <v>4316.4</v>
+        <v>0</v>
       </c>
       <c r="K140" s="4">
-        <v>3441.3</v>
+        <v>1977.86</v>
       </c>
       <c r="L140" s="4">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M140" s="4">
-        <v>42676.48</v>
+        <v>7927</v>
       </c>
       <c r="N140" s="4">
-        <v>127444.17</v>
+        <v>4916.98</v>
       </c>
     </row>
     <row r="141" spans="1:14">
@@ -6962,43 +6944,43 @@
         <v>151</v>
       </c>
       <c r="B141" s="4">
-        <v>927.514027777778</v>
+        <v>0</v>
       </c>
       <c r="C141" s="4">
-        <v>879</v>
+        <v>0</v>
       </c>
       <c r="D141" s="4">
-        <v>1426.42</v>
+        <v>0</v>
       </c>
       <c r="E141" s="4">
-        <v>927.5140277777778</v>
+        <v>0</v>
       </c>
       <c r="F141" s="4">
-        <v>6945.5</v>
+        <v>0</v>
       </c>
       <c r="G141" s="4">
-        <v>1426.42</v>
+        <v>0</v>
       </c>
       <c r="H141" s="4">
-        <v>8301.610000000001</v>
+        <v>0</v>
       </c>
       <c r="I141" s="4">
-        <v>7692.217916666668</v>
+        <v>0</v>
       </c>
       <c r="J141" s="4">
-        <v>7975.25</v>
+        <v>0</v>
       </c>
       <c r="K141" s="4">
-        <v>10155.63</v>
+        <v>0</v>
       </c>
       <c r="L141" s="4">
-        <v>42139.60069444444</v>
+        <v>0</v>
       </c>
       <c r="M141" s="4">
-        <v>54095.75</v>
+        <v>0</v>
       </c>
       <c r="N141" s="4">
-        <v>54810.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:14">
@@ -7009,40 +6991,40 @@
         <v>0</v>
       </c>
       <c r="C142" s="5">
-        <v>101.820961912705</v>
+        <v>0</v>
       </c>
       <c r="D142" s="5">
-        <v>190.6315986421832</v>
+        <v>0</v>
       </c>
       <c r="E142" s="5">
         <v>0</v>
       </c>
       <c r="F142" s="5">
-        <v>114.9353958986987</v>
+        <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>190.6315986421832</v>
+        <v>0</v>
       </c>
       <c r="H142" s="5">
-        <v>194.5164041595007</v>
+        <v>0</v>
       </c>
       <c r="I142" s="5">
-        <v>6410.181597222224</v>
+        <v>0</v>
       </c>
       <c r="J142" s="5">
-        <v>184.7662403855065</v>
+        <v>0</v>
       </c>
       <c r="K142" s="5">
-        <v>295.1102780925813</v>
+        <v>0</v>
       </c>
       <c r="L142" s="5">
-        <v>14046.53356481481</v>
+        <v>0</v>
       </c>
       <c r="M142" s="5">
-        <v>126.7577597777511</v>
+        <v>0</v>
       </c>
       <c r="N142" s="5">
-        <v>43.00709871624571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:14">
@@ -7056,7 +7038,7 @@
         <v>0</v>
       </c>
       <c r="D143" s="4">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="E143" s="4">
         <v>0</v>
@@ -7065,10 +7047,10 @@
         <v>0</v>
       </c>
       <c r="G143" s="4">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H143" s="4">
-        <v>4057.54</v>
+        <v>0</v>
       </c>
       <c r="I143" s="4">
         <v>0</v>
@@ -7077,16 +7059,16 @@
         <v>0</v>
       </c>
       <c r="K143" s="4">
-        <v>17508.17</v>
+        <v>0</v>
       </c>
       <c r="L143" s="4">
         <v>0</v>
       </c>
       <c r="M143" s="4">
-        <v>7927</v>
+        <v>0</v>
       </c>
       <c r="N143" s="4">
-        <v>21475.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:14">
@@ -7100,7 +7082,7 @@
         <v>0</v>
       </c>
       <c r="D144" s="4">
-        <v>0</v>
+        <v>194.12</v>
       </c>
       <c r="E144" s="4">
         <v>0</v>
@@ -7109,10 +7091,10 @@
         <v>0</v>
       </c>
       <c r="G144" s="4">
-        <v>0</v>
+        <v>194.12</v>
       </c>
       <c r="H144" s="4">
-        <v>0</v>
+        <v>891.25</v>
       </c>
       <c r="I144" s="4">
         <v>0</v>
@@ -7121,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="K144" s="4">
-        <v>0</v>
+        <v>418.93</v>
       </c>
       <c r="L144" s="4">
         <v>0</v>
@@ -7130,7 +7112,7 @@
         <v>0</v>
       </c>
       <c r="N144" s="4">
-        <v>0</v>
+        <v>7026.51</v>
       </c>
     </row>
     <row r="145" spans="1:14">
@@ -7218,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="N146" s="4">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="147" spans="1:14">
@@ -7229,40 +7211,40 @@
         <v>0</v>
       </c>
       <c r="C147" s="4">
-        <v>0</v>
+        <v>642.47</v>
       </c>
       <c r="D147" s="4">
-        <v>194.12</v>
+        <v>223.36</v>
       </c>
       <c r="E147" s="4">
         <v>0</v>
       </c>
       <c r="F147" s="4">
-        <v>0</v>
+        <v>5114.06</v>
       </c>
       <c r="G147" s="4">
-        <v>194.12</v>
+        <v>223.36</v>
       </c>
       <c r="H147" s="4">
-        <v>891.25</v>
+        <v>2640.92</v>
       </c>
       <c r="I147" s="4">
         <v>0</v>
       </c>
       <c r="J147" s="4">
-        <v>0</v>
+        <v>3635.07</v>
       </c>
       <c r="K147" s="4">
-        <v>418.93</v>
+        <v>1737.43</v>
       </c>
       <c r="L147" s="4">
         <v>0</v>
       </c>
       <c r="M147" s="4">
-        <v>0</v>
+        <v>47988.57</v>
       </c>
       <c r="N147" s="4">
-        <v>7026.51</v>
+        <v>23360.65</v>
       </c>
     </row>
     <row r="148" spans="1:14">
@@ -7306,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="N148" s="5">
-        <v>0</v>
+        <v>292.008125</v>
       </c>
     </row>
     <row r="149" spans="1:14">
@@ -7317,40 +7299,40 @@
         <v>0</v>
       </c>
       <c r="C149" s="4">
-        <v>0</v>
+        <v>321.12</v>
       </c>
       <c r="D149" s="4">
-        <v>0</v>
+        <v>22720</v>
       </c>
       <c r="E149" s="4">
         <v>0</v>
       </c>
       <c r="F149" s="4">
-        <v>0</v>
+        <v>2247.84</v>
       </c>
       <c r="G149" s="4">
-        <v>0</v>
+        <v>22720</v>
       </c>
       <c r="H149" s="4">
-        <v>0</v>
+        <v>97055.81</v>
       </c>
       <c r="I149" s="4">
         <v>0</v>
       </c>
       <c r="J149" s="4">
-        <v>0</v>
+        <v>1605.6</v>
       </c>
       <c r="K149" s="4">
-        <v>0</v>
+        <v>5776.89</v>
       </c>
       <c r="L149" s="4">
         <v>0</v>
       </c>
       <c r="M149" s="4">
-        <v>0</v>
+        <v>21193.92</v>
       </c>
       <c r="N149" s="4">
-        <v>8000</v>
+        <v>96377.53</v>
       </c>
     </row>
     <row r="150" spans="1:14">
@@ -7358,43 +7340,43 @@
         <v>160</v>
       </c>
       <c r="B150" s="4">
-        <v>758.2335416666667</v>
+        <v>0</v>
       </c>
       <c r="C150" s="4">
-        <v>642.47</v>
+        <v>0</v>
       </c>
       <c r="D150" s="4">
-        <v>223.36</v>
+        <v>0</v>
       </c>
       <c r="E150" s="4">
-        <v>758.2335416666667</v>
+        <v>0</v>
       </c>
       <c r="F150" s="4">
-        <v>5114.06</v>
+        <v>0</v>
       </c>
       <c r="G150" s="4">
-        <v>223.36</v>
+        <v>0</v>
       </c>
       <c r="H150" s="4">
-        <v>2640.92</v>
+        <v>0</v>
       </c>
       <c r="I150" s="4">
-        <v>3853.805152777778</v>
+        <v>0</v>
       </c>
       <c r="J150" s="4">
-        <v>3635.07</v>
+        <v>0</v>
       </c>
       <c r="K150" s="4">
-        <v>1737.43</v>
+        <v>0</v>
       </c>
       <c r="L150" s="4">
-        <v>48898.9263</v>
+        <v>0</v>
       </c>
       <c r="M150" s="4">
-        <v>47988.57</v>
+        <v>0</v>
       </c>
       <c r="N150" s="4">
-        <v>23360.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:14">
@@ -7438,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="N151" s="5">
-        <v>292.008125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:14">
@@ -7449,40 +7431,40 @@
         <v>0</v>
       </c>
       <c r="C152" s="4">
-        <v>321.12</v>
+        <v>0</v>
       </c>
       <c r="D152" s="4">
-        <v>23345.95</v>
+        <v>0</v>
       </c>
       <c r="E152" s="4">
         <v>0</v>
       </c>
       <c r="F152" s="4">
-        <v>2247.84</v>
+        <v>0</v>
       </c>
       <c r="G152" s="4">
-        <v>23345.95</v>
+        <v>0</v>
       </c>
       <c r="H152" s="4">
-        <v>124864.52</v>
+        <v>0</v>
       </c>
       <c r="I152" s="4">
         <v>0</v>
       </c>
       <c r="J152" s="4">
-        <v>1605.6</v>
+        <v>0</v>
       </c>
       <c r="K152" s="4">
-        <v>8906.639999999999</v>
+        <v>0</v>
       </c>
       <c r="L152" s="4">
         <v>0</v>
       </c>
       <c r="M152" s="4">
-        <v>21193.92</v>
+        <v>0</v>
       </c>
       <c r="N152" s="4">
-        <v>109670.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:14">
@@ -7493,40 +7475,40 @@
         <v>0</v>
       </c>
       <c r="C153" s="4">
-        <v>0</v>
+        <v>860.16</v>
       </c>
       <c r="D153" s="4">
-        <v>0</v>
+        <v>747.51</v>
       </c>
       <c r="E153" s="4">
         <v>0</v>
       </c>
       <c r="F153" s="4">
-        <v>0</v>
+        <v>5147.08</v>
       </c>
       <c r="G153" s="4">
-        <v>0</v>
+        <v>747.51</v>
       </c>
       <c r="H153" s="4">
-        <v>0</v>
+        <v>4308.91</v>
       </c>
       <c r="I153" s="4">
-        <v>0</v>
+        <v>446.5</v>
       </c>
       <c r="J153" s="4">
-        <v>0</v>
+        <v>3746.76</v>
       </c>
       <c r="K153" s="4">
-        <v>0</v>
+        <v>3024.91</v>
       </c>
       <c r="L153" s="4">
-        <v>0</v>
+        <v>1588.716666666666</v>
       </c>
       <c r="M153" s="4">
-        <v>0</v>
+        <v>46750.16</v>
       </c>
       <c r="N153" s="4">
-        <v>0</v>
+        <v>35533.97</v>
       </c>
     </row>
     <row r="154" spans="1:14">
@@ -7622,43 +7604,43 @@
         <v>166</v>
       </c>
       <c r="B156" s="4">
-        <v>770.1555111111111</v>
+        <v>0</v>
       </c>
       <c r="C156" s="4">
-        <v>860.16</v>
+        <v>1260.41</v>
       </c>
       <c r="D156" s="4">
-        <v>747.51</v>
+        <v>1142.01</v>
       </c>
       <c r="E156" s="4">
-        <v>770.1555111111111</v>
+        <v>0</v>
       </c>
       <c r="F156" s="4">
-        <v>5147.08</v>
+        <v>8662.870000000001</v>
       </c>
       <c r="G156" s="4">
-        <v>747.51</v>
+        <v>1142.01</v>
       </c>
       <c r="H156" s="4">
-        <v>4308.91</v>
+        <v>7994.07</v>
       </c>
       <c r="I156" s="4">
-        <v>3762.107144444444</v>
+        <v>0</v>
       </c>
       <c r="J156" s="4">
-        <v>3746.76</v>
+        <v>6142.05</v>
       </c>
       <c r="K156" s="4">
-        <v>3024.91</v>
+        <v>5710.05</v>
       </c>
       <c r="L156" s="4">
-        <v>47263.62762777777</v>
+        <v>0</v>
       </c>
       <c r="M156" s="4">
-        <v>46750.16</v>
+        <v>81587.06</v>
       </c>
       <c r="N156" s="4">
-        <v>35533.97</v>
+        <v>74442.57000000001</v>
       </c>
     </row>
     <row r="157" spans="1:14">
@@ -7728,7 +7710,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="4">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="I158" s="4">
         <v>0</v>
@@ -7754,43 +7736,43 @@
         <v>169</v>
       </c>
       <c r="B159" s="4">
-        <v>999.45</v>
+        <v>0</v>
       </c>
       <c r="C159" s="4">
-        <v>1260.41</v>
+        <v>988.51</v>
       </c>
       <c r="D159" s="4">
-        <v>1142.01</v>
+        <v>637.64</v>
       </c>
       <c r="E159" s="4">
-        <v>999.45</v>
+        <v>0</v>
       </c>
       <c r="F159" s="4">
-        <v>8662.870000000001</v>
+        <v>5645.97</v>
       </c>
       <c r="G159" s="4">
-        <v>1142.01</v>
+        <v>637.64</v>
       </c>
       <c r="H159" s="4">
-        <v>7994.07</v>
+        <v>4527.49</v>
       </c>
       <c r="I159" s="4">
-        <v>4997.25</v>
+        <v>0</v>
       </c>
       <c r="J159" s="4">
-        <v>6142.05</v>
+        <v>3868.95</v>
       </c>
       <c r="K159" s="4">
-        <v>5710.05</v>
+        <v>3442.05</v>
       </c>
       <c r="L159" s="4">
-        <v>65963.7</v>
+        <v>0</v>
       </c>
       <c r="M159" s="4">
-        <v>81587.06</v>
+        <v>53449.66</v>
       </c>
       <c r="N159" s="4">
-        <v>74442.57000000001</v>
+        <v>43824.72</v>
       </c>
     </row>
     <row r="160" spans="1:14">
@@ -7816,7 +7798,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="5">
-        <v>0</v>
+        <v>603.6653333333333</v>
       </c>
       <c r="I160" s="5">
         <v>0</v>
@@ -7860,7 +7842,7 @@
         <v>0</v>
       </c>
       <c r="H161" s="4">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="I161" s="4">
         <v>0</v>
@@ -7886,43 +7868,43 @@
         <v>172</v>
       </c>
       <c r="B162" s="4">
-        <v>340.1975</v>
+        <v>0</v>
       </c>
       <c r="C162" s="4">
-        <v>988.51</v>
+        <v>227.21</v>
       </c>
       <c r="D162" s="4">
-        <v>637.64</v>
+        <v>225.28</v>
       </c>
       <c r="E162" s="4">
-        <v>340.1975</v>
+        <v>0</v>
       </c>
       <c r="F162" s="4">
-        <v>5645.97</v>
+        <v>1590.47</v>
       </c>
       <c r="G162" s="4">
-        <v>637.64</v>
+        <v>225.28</v>
       </c>
       <c r="H162" s="4">
-        <v>4527.49</v>
+        <v>1576.96</v>
       </c>
       <c r="I162" s="4">
-        <v>2111.646388888889</v>
+        <v>0</v>
       </c>
       <c r="J162" s="4">
-        <v>3868.95</v>
+        <v>1136.05</v>
       </c>
       <c r="K162" s="4">
-        <v>3442.05</v>
+        <v>1126.4</v>
       </c>
       <c r="L162" s="4">
-        <v>28005.19583333334</v>
+        <v>0</v>
       </c>
       <c r="M162" s="4">
-        <v>53449.66</v>
+        <v>14995.86</v>
       </c>
       <c r="N162" s="4">
-        <v>43824.72</v>
+        <v>12930.9</v>
       </c>
     </row>
     <row r="163" spans="1:14">
@@ -7948,7 +7930,7 @@
         <v>0</v>
       </c>
       <c r="H163" s="5">
-        <v>603.6653333333333</v>
+        <v>0</v>
       </c>
       <c r="I163" s="5">
         <v>0</v>
@@ -8018,43 +8000,43 @@
         <v>175</v>
       </c>
       <c r="B165" s="4">
-        <v>398.52</v>
+        <v>0</v>
       </c>
       <c r="C165" s="4">
-        <v>227.21</v>
+        <v>849.62</v>
       </c>
       <c r="D165" s="4">
-        <v>225.28</v>
+        <v>172.19</v>
       </c>
       <c r="E165" s="4">
-        <v>398.52</v>
+        <v>0</v>
       </c>
       <c r="F165" s="4">
-        <v>1590.47</v>
+        <v>5634.22</v>
       </c>
       <c r="G165" s="4">
-        <v>225.28</v>
+        <v>172.19</v>
       </c>
       <c r="H165" s="4">
-        <v>1576.96</v>
+        <v>1822.26</v>
       </c>
       <c r="I165" s="4">
-        <v>1992.6</v>
+        <v>0</v>
       </c>
       <c r="J165" s="4">
-        <v>1136.05</v>
+        <v>3934.98</v>
       </c>
       <c r="K165" s="4">
-        <v>1126.4</v>
+        <v>1336.81</v>
       </c>
       <c r="L165" s="4">
-        <v>26302.32</v>
+        <v>0</v>
       </c>
       <c r="M165" s="4">
-        <v>14995.86</v>
+        <v>52943.72</v>
       </c>
       <c r="N165" s="4">
-        <v>12930.9</v>
+        <v>17959.17</v>
       </c>
     </row>
     <row r="166" spans="1:14">
@@ -8150,43 +8132,43 @@
         <v>178</v>
       </c>
       <c r="B168" s="4">
-        <v>853.7110388888889</v>
+        <v>0</v>
       </c>
       <c r="C168" s="4">
-        <v>849.62</v>
+        <v>0</v>
       </c>
       <c r="D168" s="4">
-        <v>172.19</v>
+        <v>0</v>
       </c>
       <c r="E168" s="4">
-        <v>853.7110388888889</v>
+        <v>0</v>
       </c>
       <c r="F168" s="4">
-        <v>5634.22</v>
+        <v>0</v>
       </c>
       <c r="G168" s="4">
-        <v>172.19</v>
+        <v>0</v>
       </c>
       <c r="H168" s="4">
-        <v>1822.26</v>
+        <v>0</v>
       </c>
       <c r="I168" s="4">
-        <v>3941.605727777778</v>
+        <v>138.67</v>
       </c>
       <c r="J168" s="4">
-        <v>3934.98</v>
+        <v>0</v>
       </c>
       <c r="K168" s="4">
-        <v>1336.81</v>
+        <v>0</v>
       </c>
       <c r="L168" s="4">
-        <v>53223.94301944444</v>
+        <v>418.925</v>
       </c>
       <c r="M168" s="4">
-        <v>52943.72</v>
+        <v>0</v>
       </c>
       <c r="N168" s="4">
-        <v>17959.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:14">
@@ -8274,7 +8256,7 @@
         <v>0</v>
       </c>
       <c r="N170" s="4">
-        <v>0</v>
+        <v>1364.14</v>
       </c>
     </row>
     <row r="171" spans="1:14">
@@ -8282,7 +8264,7 @@
         <v>181</v>
       </c>
       <c r="B171" s="4">
-        <v>175.48</v>
+        <v>0</v>
       </c>
       <c r="C171" s="4">
         <v>0</v>
@@ -8291,7 +8273,7 @@
         <v>0</v>
       </c>
       <c r="E171" s="4">
-        <v>175.48</v>
+        <v>0</v>
       </c>
       <c r="F171" s="4">
         <v>0</v>
@@ -8303,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="I171" s="4">
-        <v>877.4</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="J171" s="4">
         <v>0</v>
@@ -8312,13 +8294,13 @@
         <v>0</v>
       </c>
       <c r="L171" s="4">
-        <v>11581.68</v>
+        <v>203.83</v>
       </c>
       <c r="M171" s="4">
         <v>0</v>
       </c>
       <c r="N171" s="4">
-        <v>0</v>
+        <v>228.24</v>
       </c>
     </row>
     <row r="172" spans="1:14">
@@ -8362,447 +8344,183 @@
         <v>0</v>
       </c>
       <c r="N172" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14">
-      <c r="A173" s="2" t="s">
+        <v>16.73142052868474</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14">
+      <c r="A175" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B173" s="4">
-        <v>0</v>
-      </c>
-      <c r="C173" s="4">
-        <v>0</v>
-      </c>
-      <c r="D173" s="4">
-        <v>0</v>
-      </c>
-      <c r="E173" s="4">
-        <v>0</v>
-      </c>
-      <c r="F173" s="4">
-        <v>0</v>
-      </c>
-      <c r="G173" s="4">
-        <v>0</v>
-      </c>
-      <c r="H173" s="4">
-        <v>0</v>
-      </c>
-      <c r="I173" s="4">
-        <v>0</v>
-      </c>
-      <c r="J173" s="4">
-        <v>0</v>
-      </c>
-      <c r="K173" s="4">
-        <v>0</v>
-      </c>
-      <c r="L173" s="4">
-        <v>0</v>
-      </c>
-      <c r="M173" s="4">
-        <v>0</v>
-      </c>
-      <c r="N173" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:14">
-      <c r="A174" s="2" t="s">
+      <c r="B175" s="4">
+        <v>228727.22</v>
+      </c>
+      <c r="C175" s="4">
+        <v>335506.48</v>
+      </c>
+      <c r="D175" s="4">
+        <v>263101.1900000001</v>
+      </c>
+      <c r="E175" s="4">
+        <v>228727.22</v>
+      </c>
+      <c r="F175" s="4">
+        <v>2424435.539999999</v>
+      </c>
+      <c r="G175" s="4">
+        <v>263101.1900000001</v>
+      </c>
+      <c r="H175" s="4">
+        <v>1351697.96</v>
+      </c>
+      <c r="I175" s="4">
+        <v>1544820.77</v>
+      </c>
+      <c r="J175" s="4">
+        <v>2825129.48</v>
+      </c>
+      <c r="K175" s="4">
+        <v>1690114.89</v>
+      </c>
+      <c r="L175" s="4">
+        <v>5633355.920000001</v>
+      </c>
+      <c r="M175" s="4">
+        <v>13054804.15</v>
+      </c>
+      <c r="N175" s="4">
+        <v>7756258.590000001</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14">
+      <c r="A176" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B174" s="4">
-        <v>0</v>
-      </c>
-      <c r="C174" s="4">
-        <v>0</v>
-      </c>
-      <c r="D174" s="4">
-        <v>0</v>
-      </c>
-      <c r="E174" s="4">
-        <v>0</v>
-      </c>
-      <c r="F174" s="4">
-        <v>0</v>
-      </c>
-      <c r="G174" s="4">
-        <v>0</v>
-      </c>
-      <c r="H174" s="4">
-        <v>0</v>
-      </c>
-      <c r="I174" s="4">
-        <v>138.67</v>
-      </c>
-      <c r="J174" s="4">
-        <v>0</v>
-      </c>
-      <c r="K174" s="4">
-        <v>0</v>
-      </c>
-      <c r="L174" s="4">
-        <v>418.925</v>
-      </c>
-      <c r="M174" s="4">
-        <v>0</v>
-      </c>
-      <c r="N174" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:14">
-      <c r="A175" s="2" t="s">
+      <c r="B176" s="4">
+        <v>2930.255044444445</v>
+      </c>
+      <c r="C176" s="4">
+        <v>50293.22000000001</v>
+      </c>
+      <c r="D176" s="4">
+        <v>57620.73</v>
+      </c>
+      <c r="E176" s="4">
+        <v>2930.255044444445</v>
+      </c>
+      <c r="F176" s="4">
+        <v>346487.9799999998</v>
+      </c>
+      <c r="G176" s="4">
+        <v>57620.73</v>
+      </c>
+      <c r="H176" s="4">
+        <v>366174.4500000001</v>
+      </c>
+      <c r="I176" s="4">
+        <v>18159.03745555555</v>
+      </c>
+      <c r="J176" s="4">
+        <v>298827.79</v>
+      </c>
+      <c r="K176" s="4">
+        <v>302580.78</v>
+      </c>
+      <c r="L176" s="4">
+        <v>124223.3443444445</v>
+      </c>
+      <c r="M176" s="4">
+        <v>2645676.21</v>
+      </c>
+      <c r="N176" s="4">
+        <v>2608130.08</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14">
+      <c r="A177" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B175" s="5">
-        <v>0</v>
-      </c>
-      <c r="C175" s="5">
-        <v>0</v>
-      </c>
-      <c r="D175" s="5">
-        <v>0</v>
-      </c>
-      <c r="E175" s="5">
-        <v>0</v>
-      </c>
-      <c r="F175" s="5">
-        <v>0</v>
-      </c>
-      <c r="G175" s="5">
-        <v>0</v>
-      </c>
-      <c r="H175" s="5">
-        <v>0</v>
-      </c>
-      <c r="I175" s="5">
-        <v>0</v>
-      </c>
-      <c r="J175" s="5">
-        <v>0</v>
-      </c>
-      <c r="K175" s="5">
-        <v>0</v>
-      </c>
-      <c r="L175" s="5">
-        <v>0</v>
-      </c>
-      <c r="M175" s="5">
-        <v>0</v>
-      </c>
-      <c r="N175" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:14">
-      <c r="A176" s="2" t="s">
+      <c r="B177" s="5">
+        <v>1.281113391071008</v>
+      </c>
+      <c r="C177" s="5">
+        <v>14.99023804249623</v>
+      </c>
+      <c r="D177" s="5">
+        <v>21.90059649673192</v>
+      </c>
+      <c r="E177" s="5">
+        <v>1.281113391071008</v>
+      </c>
+      <c r="F177" s="5">
+        <v>14.29149071127706</v>
+      </c>
+      <c r="G177" s="5">
+        <v>21.90059649673192</v>
+      </c>
+      <c r="H177" s="5">
+        <v>27.08996098507097</v>
+      </c>
+      <c r="I177" s="5">
+        <v>1.175478593258139</v>
+      </c>
+      <c r="J177" s="5">
+        <v>10.57749006250857</v>
+      </c>
+      <c r="K177" s="5">
+        <v>17.90297108145116</v>
+      </c>
+      <c r="L177" s="5">
+        <v>2.205139283023403</v>
+      </c>
+      <c r="M177" s="5">
+        <v>20.26592034320178</v>
+      </c>
+      <c r="N177" s="5">
+        <v>33.62613623226298</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14">
+      <c r="A178" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B176" s="4">
-        <v>0</v>
-      </c>
-      <c r="C176" s="4">
-        <v>0</v>
-      </c>
-      <c r="D176" s="4">
-        <v>0</v>
-      </c>
-      <c r="E176" s="4">
-        <v>0</v>
-      </c>
-      <c r="F176" s="4">
-        <v>0</v>
-      </c>
-      <c r="G176" s="4">
-        <v>0</v>
-      </c>
-      <c r="H176" s="4">
-        <v>0</v>
-      </c>
-      <c r="I176" s="4">
-        <v>0</v>
-      </c>
-      <c r="J176" s="4">
-        <v>0</v>
-      </c>
-      <c r="K176" s="4">
-        <v>0</v>
-      </c>
-      <c r="L176" s="4">
-        <v>0</v>
-      </c>
-      <c r="M176" s="4">
-        <v>0</v>
-      </c>
-      <c r="N176" s="4">
-        <v>1364.14</v>
-      </c>
-    </row>
-    <row r="177" spans="1:14">
-      <c r="A177" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B177" s="4">
-        <v>0</v>
-      </c>
-      <c r="C177" s="4">
-        <v>0</v>
-      </c>
-      <c r="D177" s="4">
-        <v>0</v>
-      </c>
-      <c r="E177" s="4">
-        <v>0</v>
-      </c>
-      <c r="F177" s="4">
-        <v>0</v>
-      </c>
-      <c r="G177" s="4">
-        <v>0</v>
-      </c>
-      <c r="H177" s="4">
-        <v>0</v>
-      </c>
-      <c r="I177" s="4">
-        <v>95.93000000000001</v>
-      </c>
-      <c r="J177" s="4">
-        <v>0</v>
-      </c>
-      <c r="K177" s="4">
-        <v>0</v>
-      </c>
-      <c r="L177" s="4">
-        <v>203.83</v>
-      </c>
-      <c r="M177" s="4">
-        <v>0</v>
-      </c>
-      <c r="N177" s="4">
-        <v>228.24</v>
-      </c>
-    </row>
-    <row r="178" spans="1:14">
-      <c r="A178" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B178" s="5">
-        <v>0</v>
-      </c>
-      <c r="C178" s="5">
-        <v>0</v>
-      </c>
-      <c r="D178" s="5">
-        <v>0</v>
-      </c>
-      <c r="E178" s="5">
-        <v>0</v>
-      </c>
-      <c r="F178" s="5">
-        <v>0</v>
-      </c>
-      <c r="G178" s="5">
-        <v>0</v>
-      </c>
-      <c r="H178" s="5">
-        <v>0</v>
-      </c>
-      <c r="I178" s="5">
-        <v>0</v>
-      </c>
-      <c r="J178" s="5">
-        <v>0</v>
-      </c>
-      <c r="K178" s="5">
-        <v>0</v>
-      </c>
-      <c r="L178" s="5">
-        <v>0</v>
-      </c>
-      <c r="M178" s="5">
-        <v>0</v>
-      </c>
-      <c r="N178" s="5">
-        <v>16.73142052868474</v>
-      </c>
-    </row>
-    <row r="181" spans="1:14">
-      <c r="A181" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B181" s="4">
-        <v>228727.22</v>
-      </c>
-      <c r="C181" s="4">
-        <v>335506.48</v>
-      </c>
-      <c r="D181" s="4">
-        <v>347520.3</v>
-      </c>
-      <c r="E181" s="4">
-        <v>228727.22</v>
-      </c>
-      <c r="F181" s="4">
-        <v>2424435.539999999</v>
-      </c>
-      <c r="G181" s="4">
-        <v>347520.3</v>
-      </c>
-      <c r="H181" s="4">
-        <v>2387779.97</v>
-      </c>
-      <c r="I181" s="4">
-        <v>1544820.77</v>
-      </c>
-      <c r="J181" s="4">
-        <v>2825129.48</v>
-      </c>
-      <c r="K181" s="4">
-        <v>2782015.64</v>
-      </c>
-      <c r="L181" s="4">
-        <v>5633355.920000001</v>
-      </c>
-      <c r="M181" s="4">
-        <v>13054804.15</v>
-      </c>
-      <c r="N181" s="4">
-        <v>12759086.06</v>
-      </c>
-    </row>
-    <row r="182" spans="1:14">
-      <c r="A182" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B182" s="4">
-        <v>45825.65972222222</v>
-      </c>
-      <c r="C182" s="4">
-        <v>50293.22000000001</v>
-      </c>
-      <c r="D182" s="4">
-        <v>57620.73</v>
-      </c>
-      <c r="E182" s="4">
-        <v>45825.65972222222</v>
-      </c>
-      <c r="F182" s="4">
-        <v>346487.9799999998</v>
-      </c>
-      <c r="G182" s="4">
-        <v>57620.73</v>
-      </c>
-      <c r="H182" s="4">
-        <v>366174.4500000001</v>
-      </c>
-      <c r="I182" s="4">
-        <v>253699.3021805556</v>
-      </c>
-      <c r="J182" s="4">
-        <v>298827.79</v>
-      </c>
-      <c r="K182" s="4">
-        <v>302580.78</v>
-      </c>
-      <c r="L182" s="4">
-        <v>2384531.342569445</v>
-      </c>
-      <c r="M182" s="4">
-        <v>2645676.21</v>
-      </c>
-      <c r="N182" s="4">
-        <v>2608130.08</v>
-      </c>
-    </row>
-    <row r="183" spans="1:14">
-      <c r="A183" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B183" s="5">
-        <v>20.03507047487492</v>
-      </c>
-      <c r="C183" s="5">
-        <v>14.99023804249623</v>
-      </c>
-      <c r="D183" s="5">
-        <v>16.58053644636011</v>
-      </c>
-      <c r="E183" s="5">
-        <v>20.03507047487492</v>
-      </c>
-      <c r="F183" s="5">
-        <v>14.29149071127706</v>
-      </c>
-      <c r="G183" s="5">
-        <v>16.58053644636011</v>
-      </c>
-      <c r="H183" s="5">
-        <v>15.3353514394377</v>
-      </c>
-      <c r="I183" s="5">
-        <v>16.42257193244208</v>
-      </c>
-      <c r="J183" s="5">
-        <v>10.57749006250857</v>
-      </c>
-      <c r="K183" s="5">
-        <v>10.87631484343489</v>
-      </c>
-      <c r="L183" s="5">
-        <v>42.32878902793425</v>
-      </c>
-      <c r="M183" s="5">
-        <v>20.26592034320178</v>
-      </c>
-      <c r="N183" s="5">
-        <v>20.4413550291548</v>
-      </c>
-    </row>
-    <row r="184" spans="1:14">
-      <c r="A184" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B184" s="4">
-        <v>182901.5602777778</v>
-      </c>
-      <c r="C184" s="4">
+      <c r="B178" s="4">
+        <v>225796.9649555556</v>
+      </c>
+      <c r="C178" s="4">
         <v>285213.26</v>
       </c>
-      <c r="D184" s="4">
-        <v>289899.57</v>
-      </c>
-      <c r="E184" s="4">
-        <v>182901.5602777778</v>
-      </c>
-      <c r="F184" s="4">
+      <c r="D178" s="4">
+        <v>205480.4600000001</v>
+      </c>
+      <c r="E178" s="4">
+        <v>225796.9649555556</v>
+      </c>
+      <c r="F178" s="4">
         <v>2077947.559999999</v>
       </c>
-      <c r="G184" s="4">
-        <v>289899.57</v>
-      </c>
-      <c r="H184" s="4">
-        <v>2021605.52</v>
-      </c>
-      <c r="I184" s="4">
-        <v>1291121.467819444</v>
-      </c>
-      <c r="J184" s="4">
+      <c r="G178" s="4">
+        <v>205480.4600000001</v>
+      </c>
+      <c r="H178" s="4">
+        <v>985523.5099999998</v>
+      </c>
+      <c r="I178" s="4">
+        <v>1526661.732544445</v>
+      </c>
+      <c r="J178" s="4">
         <v>2526301.69</v>
       </c>
-      <c r="K184" s="4">
-        <v>2479434.859999999</v>
-      </c>
-      <c r="L184" s="4">
-        <v>3248824.577430556</v>
-      </c>
-      <c r="M184" s="4">
+      <c r="K178" s="4">
+        <v>1387534.11</v>
+      </c>
+      <c r="L178" s="4">
+        <v>5509132.575655556</v>
+      </c>
+      <c r="M178" s="4">
         <v>10409127.94</v>
       </c>
-      <c r="N184" s="4">
-        <v>10150955.98</v>
+      <c r="N178" s="4">
+        <v>5148128.510000001</v>
       </c>
     </row>
   </sheetData>
